--- a/public/templates/Pay-Packages-Batch-Template.xlsx
+++ b/public/templates/Pay-Packages-Batch-Template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pay Input" sheetId="1" r:id="Rbdbab4ee67024790"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="2" r:id="R28b938429e13421c"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="3" r:id="R590ece594b3340e3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Guide" sheetId="4" r:id="Rc51ea3c3bf234bc2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R7d1f680292fc4b29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="2" r:id="Rfb479e654d4940c1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples — Do Not Upload" sheetId="3" r:id="R4a42aeed2d024d65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Guide" sheetId="4" r:id="Rd812019149194287"/>
   </sheets>
 </workbook>
 </file>
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="200" formatCode="#,##0.00"/>
-    <numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
+  <numFmts count="3">
+    <numFmt numFmtId="200" formatCode="@"/>
+    <numFmt numFmtId="201" formatCode="#,##0.00"/>
+    <numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -46,7 +47,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -80,6 +81,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF64748B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
@@ -90,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -111,21 +117,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="201" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="200" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="201" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="200" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="202" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="201" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="202" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="201" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -336,6 +351,187 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="110" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="56" customHeight="1">
+      <c r="A1" s="4" t="str">
+        <v>Template type and version</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>pay-packages:1</v>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="26" t="str">
+        <v>START HERE</v>
+      </c>
+      <c r="B2" s="26" t="str">
+        <v>Fill Data Entry only. Required fields have *. Keep IDs as text; DEMO IDs are rejected. Paste values, never formulas. Field Guide explains EVERY field and gives exact choices/examples. Use Examples as a guide; replace sample details with approved facts. Upload on Payroll → Pay Packages, review the preview, then submit reviewed rows for approval. Never relabel a net agreement as Gross.</v>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="26" t="str">
+        <v>1. Use Data Entry</v>
+      </c>
+      <c r="B3" s="26" t="str">
+        <v>One continuous row contains employee, salary, net/gross agreement and allowances. No package keys. Examples and this Guide are NOT imported.</v>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="26" t="str">
+        <v>2. Approved basic pay / fee</v>
+      </c>
+      <c r="B4" s="26" t="str">
+        <v>Copy the amount and unit from Current HRIS / approved PAN or consultant agreement. Do not change approved basic salary to a guessed gross-up.</v>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="26" t="str">
+        <v>3. Existing allowances</v>
+      </c>
+      <c r="B5" s="26" t="str">
+        <v>Enter the existing HRIS de minimis and reimbursable amounts in their own columns. They must match the source; a de minimis name alone does not make it tax exempt.</v>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="26" t="str">
+        <v>4. Extra allowances</v>
+      </c>
+      <c r="B6" s="26" t="str">
+        <v>Extra 1–3 are optional. Choose a suggested name or type a custom name and amount. Recurring uses the package amount unit. One time needs a payable date. Do not repeat existing allowances here.</v>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="26" t="str">
+        <v>5. Gross salary</v>
+      </c>
+      <c r="B7" s="26" t="str">
+        <v>Agreed amount is before employee contributions and withholding. Leave Agreed net amount blank. Employer statutory shares are always separate company costs.</v>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="26" t="str">
+        <v>6. Net — covers tax</v>
+      </c>
+      <c r="B8" s="26" t="str">
+        <v>Company funds enough additional taxable compensation to meet the target before employee statutory shares. Employee shares and other authorized deductions still reduce payout.</v>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="26" t="str">
+        <v>7. Net — covers tax + shares</v>
+      </c>
+      <c r="B9" s="26" t="str">
+        <v>Company funds enough additional taxable compensation to meet the target after tax and employee statutory shares, before loans and other deductions.</v>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="26" t="str">
+        <v>8. Agreed net amount</v>
+      </c>
+      <c r="B10" s="26" t="str">
+        <v>Enter the approved target in the Amount unit of this row, separately from approved basic pay. Give the agreement reference. Finance reviews the target for each cutoff, including attendance and included allowances.</v>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="26" t="str">
+        <v>9. Tax exemption</v>
+      </c>
+      <c r="B11" s="26" t="str">
+        <v>Use Exemption requested only with legal basis and evidence. HR/Finance must classify applicable amounts and limits. Net salary does NOT exempt someone from tax. Custom rules are not automatically calculated.</v>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="26" t="str">
+        <v>10. Dual employee + consultant</v>
+      </c>
+      <c r="B12" s="26" t="str">
+        <v>Use the same employee code in two rows: Employee salary and Consultant fee. Give the consultant agreement and tax document on the consultant row. Contractor withholding remains separate. See the last two example rows.</v>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="26" t="str">
+        <v>11. Documents, not invented IDs</v>
+      </c>
+      <c r="B13" s="26" t="str">
+        <v>Type a real agreement/PAN/document reference or descriptive source note. Only PAN ID requires the actual approved HRIS PAN UUID; leave it blank for Current HRIS.</v>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="26" t="str">
+        <v>12. Dropdowns and custom text</v>
+      </c>
+      <c r="B14" s="26" t="str">
+        <v>Dropdowns suggest common choices. You may type custom allowance names, notes and document references. Employee codes and BUs must match HRIS. For different salary/tax rules choose Custom - needs review and document the terms.</v>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="26" t="str">
+        <v>13. Import and check</v>
+      </c>
+      <c r="B15" s="26" t="str">
+        <v>Payroll → Pay Packages → upload. Check every preview row before submission. Importing neither approves pay nor releases payment. Old two-tab workbooks are still supported.</v>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="26" t="str">
+        <v>14. Employer cost</v>
+      </c>
+      <c r="B16" s="26" t="str">
+        <v>Total company payroll cost = gross compensation (including company-funded gross-up) + employer statutory shares. Do not add withholding or employee contributions again; those are already inside gross.</v>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="26" t="str">
+        <v>15. Finance net calculation</v>
+      </c>
+      <c r="B17" s="26" t="str">
+        <v>Finance must confirm final monthly statutory bases including the applicable treatment of gross-up. Net calculation uses those reviewed bases and the reviewed BIR/YTD method. Recalculate if bases change; unsupported FBT cases need separate review.</v>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="26" t="str">
+        <v>BIR withholding table</v>
+      </c>
+      <c r="B18" s="26" t="str">
+        <v>https://bir-cdn.bir.gov.ph/local/pdf/Annex%20E%20RR%2011-2018.pdf</v>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="26" t="str">
+        <v>BIR tax / exemption rules</v>
+      </c>
+      <c r="B19" s="26" t="str">
+        <v>https://bir-cdn.bir.gov.ph/local/pdf/Digest%20RR%2011-2018.pdf</v>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="26" t="str">
+        <v>SSS contribution schedule</v>
+      </c>
+      <c r="B20" s="26" t="str">
+        <v>https://www.sss.gov.ph/sss-contribution-table/</v>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="26" t="str">
+        <v>PhilHealth employer procedure</v>
+      </c>
+      <c r="B21" s="26" t="str">
+        <v>https://www.philhealth.gov.ph/partners/employers/pay_procedures.php</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
@@ -386,174 +582,174 @@
   </cols>
   <sheetData>
     <row r="1" ht="58" customHeight="1">
-      <c r="A1" s="4" t="str">
-        <v>Employee code</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>Business unit</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>Pay type</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>Effective date</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>Amount unit</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>Approved basic pay / fee</v>
-      </c>
-      <c r="G1" s="5" t="str">
-        <v>Existing de minimis</v>
-      </c>
-      <c r="H1" s="5" t="str">
-        <v>Existing reimbursable</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <v>Salary arrangement</v>
-      </c>
-      <c r="J1" s="6" t="str">
-        <v>Agreed net amount</v>
-      </c>
-      <c r="K1" s="6" t="str">
-        <v>Arrangement document</v>
-      </c>
-      <c r="L1" s="6" t="str">
-        <v>Tax treatment</v>
-      </c>
-      <c r="M1" s="6" t="str">
-        <v>Exemption / tax basis</v>
-      </c>
-      <c r="N1" s="5" t="str">
-        <v>Extra 1 name</v>
-      </c>
-      <c r="O1" s="5" t="str">
-        <v>Extra 1 amount</v>
-      </c>
-      <c r="P1" s="5" t="str">
-        <v>Extra 1 frequency</v>
-      </c>
-      <c r="Q1" s="5" t="str">
-        <v>Extra 1 payable date</v>
-      </c>
-      <c r="R1" s="5" t="str">
-        <v>Extra 2 name</v>
-      </c>
-      <c r="S1" s="5" t="str">
-        <v>Extra 2 amount</v>
-      </c>
-      <c r="T1" s="5" t="str">
-        <v>Extra 2 frequency</v>
-      </c>
-      <c r="U1" s="5" t="str">
-        <v>Extra 2 payable date</v>
-      </c>
-      <c r="V1" s="5" t="str">
-        <v>Extra 3 name</v>
-      </c>
-      <c r="W1" s="5" t="str">
-        <v>Extra 3 amount</v>
-      </c>
-      <c r="X1" s="5" t="str">
-        <v>Extra 3 frequency</v>
-      </c>
-      <c r="Y1" s="5" t="str">
-        <v>Extra 3 payable date</v>
-      </c>
-      <c r="Z1" s="7" t="str">
-        <v>Salary source</v>
-      </c>
-      <c r="AA1" s="7" t="str">
-        <v>PAN ID (if applicable)</v>
-      </c>
-      <c r="AB1" s="7" t="str">
-        <v>Source document / note</v>
-      </c>
-      <c r="AC1" s="7" t="str">
-        <v>Reason for this record</v>
-      </c>
-      <c r="AD1" s="7" t="str">
-        <v>Consultant agreement</v>
-      </c>
-      <c r="AE1" s="7" t="str">
-        <v>Consultant tax document</v>
-      </c>
-      <c r="AF1" s="8" t="str">
-        <v>Employee name</v>
-      </c>
-      <c r="AG1" s="8" t="str">
-        <v>Engagement type</v>
-      </c>
-      <c r="AH1" s="8" t="str">
-        <v>Pay frequency</v>
-      </c>
-      <c r="AI1" s="8" t="str">
-        <v>Gross/net arrangement</v>
-      </c>
-      <c r="AJ1" s="8" t="str">
-        <v>Tax responsibility</v>
-      </c>
-      <c r="AK1" s="8" t="str">
-        <v>Tax coverage scope</v>
-      </c>
-      <c r="AL1" s="8" t="str">
-        <v>Benefit responsibility</v>
-      </c>
-      <c r="AM1" s="8" t="str">
-        <v>Component type</v>
-      </c>
-      <c r="AN1" s="8" t="str">
-        <v>Component name</v>
-      </c>
-      <c r="AO1" s="8" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="AP1" s="8" t="str">
-        <v>Frequency</v>
-      </c>
-      <c r="AQ1" s="8" t="str">
-        <v>Tax treatment detail</v>
-      </c>
-      <c r="AR1" s="8" t="str">
-        <v>Receipt required</v>
-      </c>
-      <c r="AS1" s="8" t="str">
-        <v>Receipt or document reference</v>
-      </c>
-      <c r="AT1" s="8" t="str">
-        <v>Policy reference</v>
-      </c>
-      <c r="AU1" s="8" t="str">
-        <v>Notes</v>
+      <c r="A1" s="8" t="str">
+        <v>Employee code*</v>
+      </c>
+      <c r="B1" s="8" t="str">
+        <v>Business unit*</v>
+      </c>
+      <c r="C1" s="8" t="str">
+        <v>Pay type*</v>
+      </c>
+      <c r="D1" s="8" t="str">
+        <v>Effective date*</v>
+      </c>
+      <c r="E1" s="8" t="str">
+        <v>Amount unit*</v>
+      </c>
+      <c r="F1" s="8" t="str">
+        <v>Approved basic pay / fee*</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>Existing de minimis (optional)</v>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v>Existing reimbursable (optional)</v>
+      </c>
+      <c r="I1" s="10" t="str">
+        <v>Salary arrangement (optional)</v>
+      </c>
+      <c r="J1" s="10" t="str">
+        <v>Agreed net amount (optional)</v>
+      </c>
+      <c r="K1" s="10" t="str">
+        <v>Arrangement document (optional)</v>
+      </c>
+      <c r="L1" s="10" t="str">
+        <v>Tax treatment (optional)</v>
+      </c>
+      <c r="M1" s="10" t="str">
+        <v>Exemption / tax basis (optional)</v>
+      </c>
+      <c r="N1" s="10" t="str">
+        <v>Extra 1 name (optional)</v>
+      </c>
+      <c r="O1" s="10" t="str">
+        <v>Extra 1 amount (optional)</v>
+      </c>
+      <c r="P1" s="10" t="str">
+        <v>Extra 1 frequency (optional)</v>
+      </c>
+      <c r="Q1" s="10" t="str">
+        <v>Extra 1 payable date (optional)</v>
+      </c>
+      <c r="R1" s="10" t="str">
+        <v>Extra 2 name (optional)</v>
+      </c>
+      <c r="S1" s="10" t="str">
+        <v>Extra 2 amount (optional)</v>
+      </c>
+      <c r="T1" s="10" t="str">
+        <v>Extra 2 frequency (optional)</v>
+      </c>
+      <c r="U1" s="10" t="str">
+        <v>Extra 2 payable date (optional)</v>
+      </c>
+      <c r="V1" s="10" t="str">
+        <v>Extra 3 name (optional)</v>
+      </c>
+      <c r="W1" s="10" t="str">
+        <v>Extra 3 amount (optional)</v>
+      </c>
+      <c r="X1" s="10" t="str">
+        <v>Extra 3 frequency (optional)</v>
+      </c>
+      <c r="Y1" s="10" t="str">
+        <v>Extra 3 payable date (optional)</v>
+      </c>
+      <c r="Z1" s="8" t="str">
+        <v>Salary source*</v>
+      </c>
+      <c r="AA1" s="10" t="str">
+        <v>PAN ID (if applicable) (optional)</v>
+      </c>
+      <c r="AB1" s="10" t="str">
+        <v>Source document / note (optional)</v>
+      </c>
+      <c r="AC1" s="8" t="str">
+        <v>Reason for this record*</v>
+      </c>
+      <c r="AD1" s="10" t="str">
+        <v>Consultant agreement (optional)</v>
+      </c>
+      <c r="AE1" s="10" t="str">
+        <v>Consultant tax document (optional)</v>
+      </c>
+      <c r="AF1" s="10" t="str">
+        <v>Employee name (optional)</v>
+      </c>
+      <c r="AG1" s="10" t="str">
+        <v>Engagement type (optional)</v>
+      </c>
+      <c r="AH1" s="10" t="str">
+        <v>Pay frequency (optional)</v>
+      </c>
+      <c r="AI1" s="10" t="str">
+        <v>Gross/net arrangement (optional)</v>
+      </c>
+      <c r="AJ1" s="10" t="str">
+        <v>Tax responsibility (optional)</v>
+      </c>
+      <c r="AK1" s="10" t="str">
+        <v>Tax coverage scope (optional)</v>
+      </c>
+      <c r="AL1" s="10" t="str">
+        <v>Benefit responsibility (optional)</v>
+      </c>
+      <c r="AM1" s="10" t="str">
+        <v>Component type (optional)</v>
+      </c>
+      <c r="AN1" s="10" t="str">
+        <v>Component name (optional)</v>
+      </c>
+      <c r="AO1" s="10" t="str">
+        <v>Amount (optional)</v>
+      </c>
+      <c r="AP1" s="10" t="str">
+        <v>Frequency (optional)</v>
+      </c>
+      <c r="AQ1" s="10" t="str">
+        <v>Tax treatment detail (optional)</v>
+      </c>
+      <c r="AR1" s="10" t="str">
+        <v>Receipt required (optional)</v>
+      </c>
+      <c r="AS1" s="10" t="str">
+        <v>Receipt or document reference (optional)</v>
+      </c>
+      <c r="AT1" s="10" t="str">
+        <v>Policy reference (optional)</v>
+      </c>
+      <c r="AU1" s="10" t="str">
+        <v>Notes (optional)</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="9"/>
+      <c r="A2" s="11"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="11"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="9"/>
-      <c r="J2" s="10"/>
+      <c r="J2" s="12"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
-      <c r="O2" s="10"/>
+      <c r="O2" s="12"/>
       <c r="P2" s="9"/>
-      <c r="Q2" s="11"/>
+      <c r="Q2" s="13"/>
       <c r="R2" s="9"/>
-      <c r="S2" s="10"/>
+      <c r="S2" s="12"/>
       <c r="T2" s="9"/>
-      <c r="U2" s="11"/>
+      <c r="U2" s="13"/>
       <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
+      <c r="W2" s="12"/>
       <c r="X2" s="9"/>
-      <c r="Y2" s="11"/>
+      <c r="Y2" s="13"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
@@ -578,31 +774,31 @@
       <c r="AU2" s="9"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="9"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="11"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="10"/>
+      <c r="J3" s="12"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
-      <c r="O3" s="10"/>
+      <c r="O3" s="12"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="11"/>
+      <c r="Q3" s="13"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="10"/>
+      <c r="S3" s="12"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="11"/>
+      <c r="U3" s="13"/>
       <c r="V3" s="9"/>
-      <c r="W3" s="10"/>
+      <c r="W3" s="12"/>
       <c r="X3" s="9"/>
-      <c r="Y3" s="11"/>
+      <c r="Y3" s="13"/>
       <c r="Z3" s="9"/>
       <c r="AA3" s="9"/>
       <c r="AB3" s="9"/>
@@ -627,31 +823,31 @@
       <c r="AU3" s="9"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="9"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="11"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="10"/>
+      <c r="O4" s="12"/>
       <c r="P4" s="9"/>
-      <c r="Q4" s="11"/>
+      <c r="Q4" s="13"/>
       <c r="R4" s="9"/>
-      <c r="S4" s="10"/>
+      <c r="S4" s="12"/>
       <c r="T4" s="9"/>
-      <c r="U4" s="11"/>
+      <c r="U4" s="13"/>
       <c r="V4" s="9"/>
-      <c r="W4" s="10"/>
+      <c r="W4" s="12"/>
       <c r="X4" s="9"/>
-      <c r="Y4" s="11"/>
+      <c r="Y4" s="13"/>
       <c r="Z4" s="9"/>
       <c r="AA4" s="9"/>
       <c r="AB4" s="9"/>
@@ -676,31 +872,31 @@
       <c r="AU4" s="9"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="9"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="10"/>
+      <c r="O5" s="12"/>
       <c r="P5" s="9"/>
-      <c r="Q5" s="11"/>
+      <c r="Q5" s="13"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="10"/>
+      <c r="S5" s="12"/>
       <c r="T5" s="9"/>
-      <c r="U5" s="11"/>
+      <c r="U5" s="13"/>
       <c r="V5" s="9"/>
-      <c r="W5" s="10"/>
+      <c r="W5" s="12"/>
       <c r="X5" s="9"/>
-      <c r="Y5" s="11"/>
+      <c r="Y5" s="13"/>
       <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
@@ -725,31 +921,31 @@
       <c r="AU5" s="9"/>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="9"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="10"/>
+      <c r="O6" s="12"/>
       <c r="P6" s="9"/>
-      <c r="Q6" s="11"/>
+      <c r="Q6" s="13"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="10"/>
+      <c r="S6" s="12"/>
       <c r="T6" s="9"/>
-      <c r="U6" s="11"/>
+      <c r="U6" s="13"/>
       <c r="V6" s="9"/>
-      <c r="W6" s="10"/>
+      <c r="W6" s="12"/>
       <c r="X6" s="9"/>
-      <c r="Y6" s="11"/>
+      <c r="Y6" s="13"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
@@ -774,31 +970,31 @@
       <c r="AU6" s="9"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="9"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="11"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="12"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="11"/>
+      <c r="Q7" s="13"/>
       <c r="R7" s="9"/>
-      <c r="S7" s="10"/>
+      <c r="S7" s="12"/>
       <c r="T7" s="9"/>
-      <c r="U7" s="11"/>
+      <c r="U7" s="13"/>
       <c r="V7" s="9"/>
-      <c r="W7" s="10"/>
+      <c r="W7" s="12"/>
       <c r="X7" s="9"/>
-      <c r="Y7" s="11"/>
+      <c r="Y7" s="13"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
@@ -823,31 +1019,31 @@
       <c r="AU7" s="9"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="9"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="11"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="J8" s="12"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="10"/>
+      <c r="O8" s="12"/>
       <c r="P8" s="9"/>
-      <c r="Q8" s="11"/>
+      <c r="Q8" s="13"/>
       <c r="R8" s="9"/>
-      <c r="S8" s="10"/>
+      <c r="S8" s="12"/>
       <c r="T8" s="9"/>
-      <c r="U8" s="11"/>
+      <c r="U8" s="13"/>
       <c r="V8" s="9"/>
-      <c r="W8" s="10"/>
+      <c r="W8" s="12"/>
       <c r="X8" s="9"/>
-      <c r="Y8" s="11"/>
+      <c r="Y8" s="13"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
       <c r="AB8" s="9"/>
@@ -872,31 +1068,31 @@
       <c r="AU8" s="9"/>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="9"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="11"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
+      <c r="J9" s="12"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
-      <c r="O9" s="10"/>
+      <c r="O9" s="12"/>
       <c r="P9" s="9"/>
-      <c r="Q9" s="11"/>
+      <c r="Q9" s="13"/>
       <c r="R9" s="9"/>
-      <c r="S9" s="10"/>
+      <c r="S9" s="12"/>
       <c r="T9" s="9"/>
-      <c r="U9" s="11"/>
+      <c r="U9" s="13"/>
       <c r="V9" s="9"/>
-      <c r="W9" s="10"/>
+      <c r="W9" s="12"/>
       <c r="X9" s="9"/>
-      <c r="Y9" s="11"/>
+      <c r="Y9" s="13"/>
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
       <c r="AB9" s="9"/>
@@ -921,31 +1117,31 @@
       <c r="AU9" s="9"/>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="9"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="11"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="J10" s="12"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="10"/>
+      <c r="O10" s="12"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="11"/>
+      <c r="Q10" s="13"/>
       <c r="R10" s="9"/>
-      <c r="S10" s="10"/>
+      <c r="S10" s="12"/>
       <c r="T10" s="9"/>
-      <c r="U10" s="11"/>
+      <c r="U10" s="13"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="10"/>
+      <c r="W10" s="12"/>
       <c r="X10" s="9"/>
-      <c r="Y10" s="11"/>
+      <c r="Y10" s="13"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
       <c r="AB10" s="9"/>
@@ -970,31 +1166,31 @@
       <c r="AU10" s="9"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="9"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="11"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
+      <c r="J11" s="12"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="10"/>
+      <c r="O11" s="12"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="11"/>
+      <c r="Q11" s="13"/>
       <c r="R11" s="9"/>
-      <c r="S11" s="10"/>
+      <c r="S11" s="12"/>
       <c r="T11" s="9"/>
-      <c r="U11" s="11"/>
+      <c r="U11" s="13"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="10"/>
+      <c r="W11" s="12"/>
       <c r="X11" s="9"/>
-      <c r="Y11" s="11"/>
+      <c r="Y11" s="13"/>
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
       <c r="AB11" s="9"/>
@@ -1019,31 +1215,31 @@
       <c r="AU11" s="9"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="9"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="11"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="12"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="13"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="10"/>
+      <c r="S12" s="12"/>
       <c r="T12" s="9"/>
-      <c r="U12" s="11"/>
+      <c r="U12" s="13"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="10"/>
+      <c r="W12" s="12"/>
       <c r="X12" s="9"/>
-      <c r="Y12" s="11"/>
+      <c r="Y12" s="13"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
       <c r="AB12" s="9"/>
@@ -1068,31 +1264,31 @@
       <c r="AU12" s="9"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="9"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="11"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="12"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="11"/>
+      <c r="Q13" s="13"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="10"/>
+      <c r="S13" s="12"/>
       <c r="T13" s="9"/>
-      <c r="U13" s="11"/>
+      <c r="U13" s="13"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="10"/>
+      <c r="W13" s="12"/>
       <c r="X13" s="9"/>
-      <c r="Y13" s="11"/>
+      <c r="Y13" s="13"/>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
@@ -1117,31 +1313,31 @@
       <c r="AU13" s="9"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="9"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="11"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
+      <c r="J14" s="12"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="10"/>
+      <c r="O14" s="12"/>
       <c r="P14" s="9"/>
-      <c r="Q14" s="11"/>
+      <c r="Q14" s="13"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="10"/>
+      <c r="S14" s="12"/>
       <c r="T14" s="9"/>
-      <c r="U14" s="11"/>
+      <c r="U14" s="13"/>
       <c r="V14" s="9"/>
-      <c r="W14" s="10"/>
+      <c r="W14" s="12"/>
       <c r="X14" s="9"/>
-      <c r="Y14" s="11"/>
+      <c r="Y14" s="13"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
       <c r="AB14" s="9"/>
@@ -1166,31 +1362,31 @@
       <c r="AU14" s="9"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="9"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="J15" s="12"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12"/>
       <c r="P15" s="9"/>
-      <c r="Q15" s="11"/>
+      <c r="Q15" s="13"/>
       <c r="R15" s="9"/>
-      <c r="S15" s="10"/>
+      <c r="S15" s="12"/>
       <c r="T15" s="9"/>
-      <c r="U15" s="11"/>
+      <c r="U15" s="13"/>
       <c r="V15" s="9"/>
-      <c r="W15" s="10"/>
+      <c r="W15" s="12"/>
       <c r="X15" s="9"/>
-      <c r="Y15" s="11"/>
+      <c r="Y15" s="13"/>
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
       <c r="AB15" s="9"/>
@@ -1215,31 +1411,31 @@
       <c r="AU15" s="9"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="9"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="11"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="12"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="10"/>
+      <c r="O16" s="12"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="11"/>
+      <c r="Q16" s="13"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="10"/>
+      <c r="S16" s="12"/>
       <c r="T16" s="9"/>
-      <c r="U16" s="11"/>
+      <c r="U16" s="13"/>
       <c r="V16" s="9"/>
-      <c r="W16" s="10"/>
+      <c r="W16" s="12"/>
       <c r="X16" s="9"/>
-      <c r="Y16" s="11"/>
+      <c r="Y16" s="13"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
       <c r="AB16" s="9"/>
@@ -1264,31 +1460,31 @@
       <c r="AU16" s="9"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="9"/>
+      <c r="A17" s="11"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="11"/>
+      <c r="D17" s="13"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
+      <c r="J17" s="12"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="10"/>
+      <c r="O17" s="12"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="11"/>
+      <c r="Q17" s="13"/>
       <c r="R17" s="9"/>
-      <c r="S17" s="10"/>
+      <c r="S17" s="12"/>
       <c r="T17" s="9"/>
-      <c r="U17" s="11"/>
+      <c r="U17" s="13"/>
       <c r="V17" s="9"/>
-      <c r="W17" s="10"/>
+      <c r="W17" s="12"/>
       <c r="X17" s="9"/>
-      <c r="Y17" s="11"/>
+      <c r="Y17" s="13"/>
       <c r="Z17" s="9"/>
       <c r="AA17" s="9"/>
       <c r="AB17" s="9"/>
@@ -1313,31 +1509,31 @@
       <c r="AU17" s="9"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="9"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
-      <c r="D18" s="11"/>
+      <c r="D18" s="13"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
+      <c r="J18" s="12"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="10"/>
+      <c r="O18" s="12"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="11"/>
+      <c r="Q18" s="13"/>
       <c r="R18" s="9"/>
-      <c r="S18" s="10"/>
+      <c r="S18" s="12"/>
       <c r="T18" s="9"/>
-      <c r="U18" s="11"/>
+      <c r="U18" s="13"/>
       <c r="V18" s="9"/>
-      <c r="W18" s="10"/>
+      <c r="W18" s="12"/>
       <c r="X18" s="9"/>
-      <c r="Y18" s="11"/>
+      <c r="Y18" s="13"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="9"/>
       <c r="AB18" s="9"/>
@@ -1362,31 +1558,31 @@
       <c r="AU18" s="9"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="9"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="11"/>
+      <c r="D19" s="13"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
+      <c r="J19" s="12"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="12"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="11"/>
+      <c r="Q19" s="13"/>
       <c r="R19" s="9"/>
-      <c r="S19" s="10"/>
+      <c r="S19" s="12"/>
       <c r="T19" s="9"/>
-      <c r="U19" s="11"/>
+      <c r="U19" s="13"/>
       <c r="V19" s="9"/>
-      <c r="W19" s="10"/>
+      <c r="W19" s="12"/>
       <c r="X19" s="9"/>
-      <c r="Y19" s="11"/>
+      <c r="Y19" s="13"/>
       <c r="Z19" s="9"/>
       <c r="AA19" s="9"/>
       <c r="AB19" s="9"/>
@@ -1411,31 +1607,31 @@
       <c r="AU19" s="9"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="9"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="11"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
+      <c r="J20" s="12"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="10"/>
+      <c r="O20" s="12"/>
       <c r="P20" s="9"/>
-      <c r="Q20" s="11"/>
+      <c r="Q20" s="13"/>
       <c r="R20" s="9"/>
-      <c r="S20" s="10"/>
+      <c r="S20" s="12"/>
       <c r="T20" s="9"/>
-      <c r="U20" s="11"/>
+      <c r="U20" s="13"/>
       <c r="V20" s="9"/>
-      <c r="W20" s="10"/>
+      <c r="W20" s="12"/>
       <c r="X20" s="9"/>
-      <c r="Y20" s="11"/>
+      <c r="Y20" s="13"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="9"/>
       <c r="AB20" s="9"/>
@@ -1460,31 +1656,31 @@
       <c r="AU20" s="9"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="9"/>
+      <c r="A21" s="11"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
-      <c r="D21" s="11"/>
+      <c r="D21" s="13"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
+      <c r="J21" s="12"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="10"/>
+      <c r="O21" s="12"/>
       <c r="P21" s="9"/>
-      <c r="Q21" s="11"/>
+      <c r="Q21" s="13"/>
       <c r="R21" s="9"/>
-      <c r="S21" s="10"/>
+      <c r="S21" s="12"/>
       <c r="T21" s="9"/>
-      <c r="U21" s="11"/>
+      <c r="U21" s="13"/>
       <c r="V21" s="9"/>
-      <c r="W21" s="10"/>
+      <c r="W21" s="12"/>
       <c r="X21" s="9"/>
-      <c r="Y21" s="11"/>
+      <c r="Y21" s="13"/>
       <c r="Z21" s="9"/>
       <c r="AA21" s="9"/>
       <c r="AB21" s="9"/>
@@ -1509,31 +1705,31 @@
       <c r="AU21" s="9"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="9"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
-      <c r="D22" s="11"/>
+      <c r="D22" s="13"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
+      <c r="J22" s="12"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="10"/>
+      <c r="O22" s="12"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="11"/>
+      <c r="Q22" s="13"/>
       <c r="R22" s="9"/>
-      <c r="S22" s="10"/>
+      <c r="S22" s="12"/>
       <c r="T22" s="9"/>
-      <c r="U22" s="11"/>
+      <c r="U22" s="13"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="10"/>
+      <c r="W22" s="12"/>
       <c r="X22" s="9"/>
-      <c r="Y22" s="11"/>
+      <c r="Y22" s="13"/>
       <c r="Z22" s="9"/>
       <c r="AA22" s="9"/>
       <c r="AB22" s="9"/>
@@ -1558,31 +1754,31 @@
       <c r="AU22" s="9"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="9"/>
+      <c r="A23" s="11"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="11"/>
+      <c r="D23" s="13"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="10"/>
+      <c r="O23" s="12"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="11"/>
+      <c r="Q23" s="13"/>
       <c r="R23" s="9"/>
-      <c r="S23" s="10"/>
+      <c r="S23" s="12"/>
       <c r="T23" s="9"/>
-      <c r="U23" s="11"/>
+      <c r="U23" s="13"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="10"/>
+      <c r="W23" s="12"/>
       <c r="X23" s="9"/>
-      <c r="Y23" s="11"/>
+      <c r="Y23" s="13"/>
       <c r="Z23" s="9"/>
       <c r="AA23" s="9"/>
       <c r="AB23" s="9"/>
@@ -1607,31 +1803,31 @@
       <c r="AU23" s="9"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="9"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="11"/>
+      <c r="D24" s="13"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
+      <c r="J24" s="12"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="10"/>
+      <c r="O24" s="12"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="11"/>
+      <c r="Q24" s="13"/>
       <c r="R24" s="9"/>
-      <c r="S24" s="10"/>
+      <c r="S24" s="12"/>
       <c r="T24" s="9"/>
-      <c r="U24" s="11"/>
+      <c r="U24" s="13"/>
       <c r="V24" s="9"/>
-      <c r="W24" s="10"/>
+      <c r="W24" s="12"/>
       <c r="X24" s="9"/>
-      <c r="Y24" s="11"/>
+      <c r="Y24" s="13"/>
       <c r="Z24" s="9"/>
       <c r="AA24" s="9"/>
       <c r="AB24" s="9"/>
@@ -1656,31 +1852,31 @@
       <c r="AU24" s="9"/>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="9"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="11"/>
+      <c r="D25" s="13"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
       <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
+      <c r="J25" s="12"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="10"/>
+      <c r="O25" s="12"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="11"/>
+      <c r="Q25" s="13"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="10"/>
+      <c r="S25" s="12"/>
       <c r="T25" s="9"/>
-      <c r="U25" s="11"/>
+      <c r="U25" s="13"/>
       <c r="V25" s="9"/>
-      <c r="W25" s="10"/>
+      <c r="W25" s="12"/>
       <c r="X25" s="9"/>
-      <c r="Y25" s="11"/>
+      <c r="Y25" s="13"/>
       <c r="Z25" s="9"/>
       <c r="AA25" s="9"/>
       <c r="AB25" s="9"/>
@@ -1705,31 +1901,31 @@
       <c r="AU25" s="9"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="9"/>
+      <c r="A26" s="11"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="11"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
+      <c r="J26" s="12"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="10"/>
+      <c r="O26" s="12"/>
       <c r="P26" s="9"/>
-      <c r="Q26" s="11"/>
+      <c r="Q26" s="13"/>
       <c r="R26" s="9"/>
-      <c r="S26" s="10"/>
+      <c r="S26" s="12"/>
       <c r="T26" s="9"/>
-      <c r="U26" s="11"/>
+      <c r="U26" s="13"/>
       <c r="V26" s="9"/>
-      <c r="W26" s="10"/>
+      <c r="W26" s="12"/>
       <c r="X26" s="9"/>
-      <c r="Y26" s="11"/>
+      <c r="Y26" s="13"/>
       <c r="Z26" s="9"/>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
@@ -1754,31 +1950,31 @@
       <c r="AU26" s="9"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="9"/>
+      <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="11"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
+      <c r="J27" s="12"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="10"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="9"/>
-      <c r="Q27" s="11"/>
+      <c r="Q27" s="13"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="10"/>
+      <c r="S27" s="12"/>
       <c r="T27" s="9"/>
-      <c r="U27" s="11"/>
+      <c r="U27" s="13"/>
       <c r="V27" s="9"/>
-      <c r="W27" s="10"/>
+      <c r="W27" s="12"/>
       <c r="X27" s="9"/>
-      <c r="Y27" s="11"/>
+      <c r="Y27" s="13"/>
       <c r="Z27" s="9"/>
       <c r="AA27" s="9"/>
       <c r="AB27" s="9"/>
@@ -1803,31 +1999,31 @@
       <c r="AU27" s="9"/>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="9"/>
+      <c r="A28" s="11"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="11"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
       <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
+      <c r="J28" s="12"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="10"/>
+      <c r="O28" s="12"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="11"/>
+      <c r="Q28" s="13"/>
       <c r="R28" s="9"/>
-      <c r="S28" s="10"/>
+      <c r="S28" s="12"/>
       <c r="T28" s="9"/>
-      <c r="U28" s="11"/>
+      <c r="U28" s="13"/>
       <c r="V28" s="9"/>
-      <c r="W28" s="10"/>
+      <c r="W28" s="12"/>
       <c r="X28" s="9"/>
-      <c r="Y28" s="11"/>
+      <c r="Y28" s="13"/>
       <c r="Z28" s="9"/>
       <c r="AA28" s="9"/>
       <c r="AB28" s="9"/>
@@ -1852,31 +2048,31 @@
       <c r="AU28" s="9"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="9"/>
+      <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="11"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
       <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
+      <c r="J29" s="12"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="10"/>
+      <c r="O29" s="12"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="11"/>
+      <c r="Q29" s="13"/>
       <c r="R29" s="9"/>
-      <c r="S29" s="10"/>
+      <c r="S29" s="12"/>
       <c r="T29" s="9"/>
-      <c r="U29" s="11"/>
+      <c r="U29" s="13"/>
       <c r="V29" s="9"/>
-      <c r="W29" s="10"/>
+      <c r="W29" s="12"/>
       <c r="X29" s="9"/>
-      <c r="Y29" s="11"/>
+      <c r="Y29" s="13"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
@@ -1901,31 +2097,31 @@
       <c r="AU29" s="9"/>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="9"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="11"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
       <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
+      <c r="J30" s="12"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="10"/>
+      <c r="O30" s="12"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="11"/>
+      <c r="Q30" s="13"/>
       <c r="R30" s="9"/>
-      <c r="S30" s="10"/>
+      <c r="S30" s="12"/>
       <c r="T30" s="9"/>
-      <c r="U30" s="11"/>
+      <c r="U30" s="13"/>
       <c r="V30" s="9"/>
-      <c r="W30" s="10"/>
+      <c r="W30" s="12"/>
       <c r="X30" s="9"/>
-      <c r="Y30" s="11"/>
+      <c r="Y30" s="13"/>
       <c r="Z30" s="9"/>
       <c r="AA30" s="9"/>
       <c r="AB30" s="9"/>
@@ -1950,31 +2146,31 @@
       <c r="AU30" s="9"/>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="9"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="11"/>
+      <c r="D31" s="13"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
       <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
+      <c r="J31" s="12"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="10"/>
+      <c r="O31" s="12"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="11"/>
+      <c r="Q31" s="13"/>
       <c r="R31" s="9"/>
-      <c r="S31" s="10"/>
+      <c r="S31" s="12"/>
       <c r="T31" s="9"/>
-      <c r="U31" s="11"/>
+      <c r="U31" s="13"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="10"/>
+      <c r="W31" s="12"/>
       <c r="X31" s="9"/>
-      <c r="Y31" s="11"/>
+      <c r="Y31" s="13"/>
       <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
       <c r="AB31" s="9"/>
@@ -1999,31 +2195,31 @@
       <c r="AU31" s="9"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="9"/>
+      <c r="A32" s="11"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="11"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
+      <c r="J32" s="12"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="10"/>
+      <c r="O32" s="12"/>
       <c r="P32" s="9"/>
-      <c r="Q32" s="11"/>
+      <c r="Q32" s="13"/>
       <c r="R32" s="9"/>
-      <c r="S32" s="10"/>
+      <c r="S32" s="12"/>
       <c r="T32" s="9"/>
-      <c r="U32" s="11"/>
+      <c r="U32" s="13"/>
       <c r="V32" s="9"/>
-      <c r="W32" s="10"/>
+      <c r="W32" s="12"/>
       <c r="X32" s="9"/>
-      <c r="Y32" s="11"/>
+      <c r="Y32" s="13"/>
       <c r="Z32" s="9"/>
       <c r="AA32" s="9"/>
       <c r="AB32" s="9"/>
@@ -2048,31 +2244,31 @@
       <c r="AU32" s="9"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="9"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="11"/>
+      <c r="D33" s="13"/>
       <c r="E33" s="9"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
+      <c r="J33" s="12"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="10"/>
+      <c r="O33" s="12"/>
       <c r="P33" s="9"/>
-      <c r="Q33" s="11"/>
+      <c r="Q33" s="13"/>
       <c r="R33" s="9"/>
-      <c r="S33" s="10"/>
+      <c r="S33" s="12"/>
       <c r="T33" s="9"/>
-      <c r="U33" s="11"/>
+      <c r="U33" s="13"/>
       <c r="V33" s="9"/>
-      <c r="W33" s="10"/>
+      <c r="W33" s="12"/>
       <c r="X33" s="9"/>
-      <c r="Y33" s="11"/>
+      <c r="Y33" s="13"/>
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
       <c r="AB33" s="9"/>
@@ -2097,31 +2293,31 @@
       <c r="AU33" s="9"/>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="9"/>
+      <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="11"/>
+      <c r="D34" s="13"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="10"/>
+      <c r="J34" s="12"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="10"/>
+      <c r="O34" s="12"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="11"/>
+      <c r="Q34" s="13"/>
       <c r="R34" s="9"/>
-      <c r="S34" s="10"/>
+      <c r="S34" s="12"/>
       <c r="T34" s="9"/>
-      <c r="U34" s="11"/>
+      <c r="U34" s="13"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="10"/>
+      <c r="W34" s="12"/>
       <c r="X34" s="9"/>
-      <c r="Y34" s="11"/>
+      <c r="Y34" s="13"/>
       <c r="Z34" s="9"/>
       <c r="AA34" s="9"/>
       <c r="AB34" s="9"/>
@@ -2146,31 +2342,31 @@
       <c r="AU34" s="9"/>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="9"/>
+      <c r="A35" s="11"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="11"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="9"/>
-      <c r="J35" s="10"/>
+      <c r="J35" s="12"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="10"/>
+      <c r="O35" s="12"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="11"/>
+      <c r="Q35" s="13"/>
       <c r="R35" s="9"/>
-      <c r="S35" s="10"/>
+      <c r="S35" s="12"/>
       <c r="T35" s="9"/>
-      <c r="U35" s="11"/>
+      <c r="U35" s="13"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="10"/>
+      <c r="W35" s="12"/>
       <c r="X35" s="9"/>
-      <c r="Y35" s="11"/>
+      <c r="Y35" s="13"/>
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
       <c r="AB35" s="9"/>
@@ -2195,31 +2391,31 @@
       <c r="AU35" s="9"/>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="9"/>
+      <c r="A36" s="11"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="11"/>
+      <c r="D36" s="13"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="10"/>
+      <c r="J36" s="12"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="10"/>
+      <c r="O36" s="12"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="11"/>
+      <c r="Q36" s="13"/>
       <c r="R36" s="9"/>
-      <c r="S36" s="10"/>
+      <c r="S36" s="12"/>
       <c r="T36" s="9"/>
-      <c r="U36" s="11"/>
+      <c r="U36" s="13"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="10"/>
+      <c r="W36" s="12"/>
       <c r="X36" s="9"/>
-      <c r="Y36" s="11"/>
+      <c r="Y36" s="13"/>
       <c r="Z36" s="9"/>
       <c r="AA36" s="9"/>
       <c r="AB36" s="9"/>
@@ -2244,31 +2440,31 @@
       <c r="AU36" s="9"/>
     </row>
     <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="9"/>
+      <c r="A37" s="11"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="11"/>
+      <c r="D37" s="13"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="10"/>
+      <c r="J37" s="12"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
-      <c r="O37" s="10"/>
+      <c r="O37" s="12"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="11"/>
+      <c r="Q37" s="13"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="10"/>
+      <c r="S37" s="12"/>
       <c r="T37" s="9"/>
-      <c r="U37" s="11"/>
+      <c r="U37" s="13"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="10"/>
+      <c r="W37" s="12"/>
       <c r="X37" s="9"/>
-      <c r="Y37" s="11"/>
+      <c r="Y37" s="13"/>
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
       <c r="AB37" s="9"/>
@@ -2293,31 +2489,31 @@
       <c r="AU37" s="9"/>
     </row>
     <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="9"/>
+      <c r="A38" s="11"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="11"/>
+      <c r="D38" s="13"/>
       <c r="E38" s="9"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
       <c r="I38" s="9"/>
-      <c r="J38" s="10"/>
+      <c r="J38" s="12"/>
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="10"/>
+      <c r="O38" s="12"/>
       <c r="P38" s="9"/>
-      <c r="Q38" s="11"/>
+      <c r="Q38" s="13"/>
       <c r="R38" s="9"/>
-      <c r="S38" s="10"/>
+      <c r="S38" s="12"/>
       <c r="T38" s="9"/>
-      <c r="U38" s="11"/>
+      <c r="U38" s="13"/>
       <c r="V38" s="9"/>
-      <c r="W38" s="10"/>
+      <c r="W38" s="12"/>
       <c r="X38" s="9"/>
-      <c r="Y38" s="11"/>
+      <c r="Y38" s="13"/>
       <c r="Z38" s="9"/>
       <c r="AA38" s="9"/>
       <c r="AB38" s="9"/>
@@ -2342,31 +2538,31 @@
       <c r="AU38" s="9"/>
     </row>
     <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="9"/>
+      <c r="A39" s="11"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="11"/>
+      <c r="D39" s="13"/>
       <c r="E39" s="9"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
       <c r="I39" s="9"/>
-      <c r="J39" s="10"/>
+      <c r="J39" s="12"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
       <c r="N39" s="9"/>
-      <c r="O39" s="10"/>
+      <c r="O39" s="12"/>
       <c r="P39" s="9"/>
-      <c r="Q39" s="11"/>
+      <c r="Q39" s="13"/>
       <c r="R39" s="9"/>
-      <c r="S39" s="10"/>
+      <c r="S39" s="12"/>
       <c r="T39" s="9"/>
-      <c r="U39" s="11"/>
+      <c r="U39" s="13"/>
       <c r="V39" s="9"/>
-      <c r="W39" s="10"/>
+      <c r="W39" s="12"/>
       <c r="X39" s="9"/>
-      <c r="Y39" s="11"/>
+      <c r="Y39" s="13"/>
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
       <c r="AB39" s="9"/>
@@ -2391,31 +2587,31 @@
       <c r="AU39" s="9"/>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="9"/>
+      <c r="A40" s="11"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="11"/>
+      <c r="D40" s="13"/>
       <c r="E40" s="9"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="10"/>
+      <c r="J40" s="12"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="10"/>
+      <c r="O40" s="12"/>
       <c r="P40" s="9"/>
-      <c r="Q40" s="11"/>
+      <c r="Q40" s="13"/>
       <c r="R40" s="9"/>
-      <c r="S40" s="10"/>
+      <c r="S40" s="12"/>
       <c r="T40" s="9"/>
-      <c r="U40" s="11"/>
+      <c r="U40" s="13"/>
       <c r="V40" s="9"/>
-      <c r="W40" s="10"/>
+      <c r="W40" s="12"/>
       <c r="X40" s="9"/>
-      <c r="Y40" s="11"/>
+      <c r="Y40" s="13"/>
       <c r="Z40" s="9"/>
       <c r="AA40" s="9"/>
       <c r="AB40" s="9"/>
@@ -2440,31 +2636,31 @@
       <c r="AU40" s="9"/>
     </row>
     <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="9"/>
+      <c r="A41" s="11"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="11"/>
+      <c r="D41" s="13"/>
       <c r="E41" s="9"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
       <c r="I41" s="9"/>
-      <c r="J41" s="10"/>
+      <c r="J41" s="12"/>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
-      <c r="O41" s="10"/>
+      <c r="O41" s="12"/>
       <c r="P41" s="9"/>
-      <c r="Q41" s="11"/>
+      <c r="Q41" s="13"/>
       <c r="R41" s="9"/>
-      <c r="S41" s="10"/>
+      <c r="S41" s="12"/>
       <c r="T41" s="9"/>
-      <c r="U41" s="11"/>
+      <c r="U41" s="13"/>
       <c r="V41" s="9"/>
-      <c r="W41" s="10"/>
+      <c r="W41" s="12"/>
       <c r="X41" s="9"/>
-      <c r="Y41" s="11"/>
+      <c r="Y41" s="13"/>
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
       <c r="AB41" s="9"/>
@@ -2489,31 +2685,31 @@
       <c r="AU41" s="9"/>
     </row>
     <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="9"/>
+      <c r="A42" s="11"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="11"/>
+      <c r="D42" s="13"/>
       <c r="E42" s="9"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
       <c r="I42" s="9"/>
-      <c r="J42" s="10"/>
+      <c r="J42" s="12"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
-      <c r="O42" s="10"/>
+      <c r="O42" s="12"/>
       <c r="P42" s="9"/>
-      <c r="Q42" s="11"/>
+      <c r="Q42" s="13"/>
       <c r="R42" s="9"/>
-      <c r="S42" s="10"/>
+      <c r="S42" s="12"/>
       <c r="T42" s="9"/>
-      <c r="U42" s="11"/>
+      <c r="U42" s="13"/>
       <c r="V42" s="9"/>
-      <c r="W42" s="10"/>
+      <c r="W42" s="12"/>
       <c r="X42" s="9"/>
-      <c r="Y42" s="11"/>
+      <c r="Y42" s="13"/>
       <c r="Z42" s="9"/>
       <c r="AA42" s="9"/>
       <c r="AB42" s="9"/>
@@ -2538,31 +2734,31 @@
       <c r="AU42" s="9"/>
     </row>
     <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="9"/>
+      <c r="A43" s="11"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="11"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="9"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
       <c r="I43" s="9"/>
-      <c r="J43" s="10"/>
+      <c r="J43" s="12"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
-      <c r="O43" s="10"/>
+      <c r="O43" s="12"/>
       <c r="P43" s="9"/>
-      <c r="Q43" s="11"/>
+      <c r="Q43" s="13"/>
       <c r="R43" s="9"/>
-      <c r="S43" s="10"/>
+      <c r="S43" s="12"/>
       <c r="T43" s="9"/>
-      <c r="U43" s="11"/>
+      <c r="U43" s="13"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="10"/>
+      <c r="W43" s="12"/>
       <c r="X43" s="9"/>
-      <c r="Y43" s="11"/>
+      <c r="Y43" s="13"/>
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
@@ -2587,31 +2783,31 @@
       <c r="AU43" s="9"/>
     </row>
     <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="9"/>
+      <c r="A44" s="11"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="11"/>
+      <c r="D44" s="13"/>
       <c r="E44" s="9"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
       <c r="I44" s="9"/>
-      <c r="J44" s="10"/>
+      <c r="J44" s="12"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
-      <c r="O44" s="10"/>
+      <c r="O44" s="12"/>
       <c r="P44" s="9"/>
-      <c r="Q44" s="11"/>
+      <c r="Q44" s="13"/>
       <c r="R44" s="9"/>
-      <c r="S44" s="10"/>
+      <c r="S44" s="12"/>
       <c r="T44" s="9"/>
-      <c r="U44" s="11"/>
+      <c r="U44" s="13"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="10"/>
+      <c r="W44" s="12"/>
       <c r="X44" s="9"/>
-      <c r="Y44" s="11"/>
+      <c r="Y44" s="13"/>
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
       <c r="AB44" s="9"/>
@@ -2636,31 +2832,31 @@
       <c r="AU44" s="9"/>
     </row>
     <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="9"/>
+      <c r="A45" s="11"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="11"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="9"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
       <c r="I45" s="9"/>
-      <c r="J45" s="10"/>
+      <c r="J45" s="12"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
-      <c r="O45" s="10"/>
+      <c r="O45" s="12"/>
       <c r="P45" s="9"/>
-      <c r="Q45" s="11"/>
+      <c r="Q45" s="13"/>
       <c r="R45" s="9"/>
-      <c r="S45" s="10"/>
+      <c r="S45" s="12"/>
       <c r="T45" s="9"/>
-      <c r="U45" s="11"/>
+      <c r="U45" s="13"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="10"/>
+      <c r="W45" s="12"/>
       <c r="X45" s="9"/>
-      <c r="Y45" s="11"/>
+      <c r="Y45" s="13"/>
       <c r="Z45" s="9"/>
       <c r="AA45" s="9"/>
       <c r="AB45" s="9"/>
@@ -2685,31 +2881,31 @@
       <c r="AU45" s="9"/>
     </row>
     <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="9"/>
+      <c r="A46" s="11"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="11"/>
+      <c r="D46" s="13"/>
       <c r="E46" s="9"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
       <c r="I46" s="9"/>
-      <c r="J46" s="10"/>
+      <c r="J46" s="12"/>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
       <c r="N46" s="9"/>
-      <c r="O46" s="10"/>
+      <c r="O46" s="12"/>
       <c r="P46" s="9"/>
-      <c r="Q46" s="11"/>
+      <c r="Q46" s="13"/>
       <c r="R46" s="9"/>
-      <c r="S46" s="10"/>
+      <c r="S46" s="12"/>
       <c r="T46" s="9"/>
-      <c r="U46" s="11"/>
+      <c r="U46" s="13"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="10"/>
+      <c r="W46" s="12"/>
       <c r="X46" s="9"/>
-      <c r="Y46" s="11"/>
+      <c r="Y46" s="13"/>
       <c r="Z46" s="9"/>
       <c r="AA46" s="9"/>
       <c r="AB46" s="9"/>
@@ -2734,31 +2930,31 @@
       <c r="AU46" s="9"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="9"/>
+      <c r="A47" s="11"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="11"/>
+      <c r="D47" s="13"/>
       <c r="E47" s="9"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
       <c r="I47" s="9"/>
-      <c r="J47" s="10"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9"/>
       <c r="N47" s="9"/>
-      <c r="O47" s="10"/>
+      <c r="O47" s="12"/>
       <c r="P47" s="9"/>
-      <c r="Q47" s="11"/>
+      <c r="Q47" s="13"/>
       <c r="R47" s="9"/>
-      <c r="S47" s="10"/>
+      <c r="S47" s="12"/>
       <c r="T47" s="9"/>
-      <c r="U47" s="11"/>
+      <c r="U47" s="13"/>
       <c r="V47" s="9"/>
-      <c r="W47" s="10"/>
+      <c r="W47" s="12"/>
       <c r="X47" s="9"/>
-      <c r="Y47" s="11"/>
+      <c r="Y47" s="13"/>
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
       <c r="AB47" s="9"/>
@@ -2783,31 +2979,31 @@
       <c r="AU47" s="9"/>
     </row>
     <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="9"/>
+      <c r="A48" s="11"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="11"/>
+      <c r="D48" s="13"/>
       <c r="E48" s="9"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
       <c r="I48" s="9"/>
-      <c r="J48" s="10"/>
+      <c r="J48" s="12"/>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
-      <c r="O48" s="10"/>
+      <c r="O48" s="12"/>
       <c r="P48" s="9"/>
-      <c r="Q48" s="11"/>
+      <c r="Q48" s="13"/>
       <c r="R48" s="9"/>
-      <c r="S48" s="10"/>
+      <c r="S48" s="12"/>
       <c r="T48" s="9"/>
-      <c r="U48" s="11"/>
+      <c r="U48" s="13"/>
       <c r="V48" s="9"/>
-      <c r="W48" s="10"/>
+      <c r="W48" s="12"/>
       <c r="X48" s="9"/>
-      <c r="Y48" s="11"/>
+      <c r="Y48" s="13"/>
       <c r="Z48" s="9"/>
       <c r="AA48" s="9"/>
       <c r="AB48" s="9"/>
@@ -2832,31 +3028,31 @@
       <c r="AU48" s="9"/>
     </row>
     <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="9"/>
+      <c r="A49" s="11"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="11"/>
+      <c r="D49" s="13"/>
       <c r="E49" s="9"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
       <c r="I49" s="9"/>
-      <c r="J49" s="10"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
-      <c r="O49" s="10"/>
+      <c r="O49" s="12"/>
       <c r="P49" s="9"/>
-      <c r="Q49" s="11"/>
+      <c r="Q49" s="13"/>
       <c r="R49" s="9"/>
-      <c r="S49" s="10"/>
+      <c r="S49" s="12"/>
       <c r="T49" s="9"/>
-      <c r="U49" s="11"/>
+      <c r="U49" s="13"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="10"/>
+      <c r="W49" s="12"/>
       <c r="X49" s="9"/>
-      <c r="Y49" s="11"/>
+      <c r="Y49" s="13"/>
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
       <c r="AB49" s="9"/>
@@ -2881,31 +3077,31 @@
       <c r="AU49" s="9"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="9"/>
+      <c r="A50" s="11"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="11"/>
+      <c r="D50" s="13"/>
       <c r="E50" s="9"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
       <c r="I50" s="9"/>
-      <c r="J50" s="10"/>
+      <c r="J50" s="12"/>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="9"/>
-      <c r="O50" s="10"/>
+      <c r="O50" s="12"/>
       <c r="P50" s="9"/>
-      <c r="Q50" s="11"/>
+      <c r="Q50" s="13"/>
       <c r="R50" s="9"/>
-      <c r="S50" s="10"/>
+      <c r="S50" s="12"/>
       <c r="T50" s="9"/>
-      <c r="U50" s="11"/>
+      <c r="U50" s="13"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="10"/>
+      <c r="W50" s="12"/>
       <c r="X50" s="9"/>
-      <c r="Y50" s="11"/>
+      <c r="Y50" s="13"/>
       <c r="Z50" s="9"/>
       <c r="AA50" s="9"/>
       <c r="AB50" s="9"/>
@@ -2930,31 +3126,31 @@
       <c r="AU50" s="9"/>
     </row>
     <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="9"/>
+      <c r="A51" s="11"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="11"/>
+      <c r="D51" s="13"/>
       <c r="E51" s="9"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
       <c r="I51" s="9"/>
-      <c r="J51" s="10"/>
+      <c r="J51" s="12"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
       <c r="N51" s="9"/>
-      <c r="O51" s="10"/>
+      <c r="O51" s="12"/>
       <c r="P51" s="9"/>
-      <c r="Q51" s="11"/>
+      <c r="Q51" s="13"/>
       <c r="R51" s="9"/>
-      <c r="S51" s="10"/>
+      <c r="S51" s="12"/>
       <c r="T51" s="9"/>
-      <c r="U51" s="11"/>
+      <c r="U51" s="13"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="10"/>
+      <c r="W51" s="12"/>
       <c r="X51" s="9"/>
-      <c r="Y51" s="11"/>
+      <c r="Y51" s="13"/>
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
       <c r="AB51" s="9"/>
@@ -2979,31 +3175,31 @@
       <c r="AU51" s="9"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="9"/>
+      <c r="A52" s="11"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="11"/>
+      <c r="D52" s="13"/>
       <c r="E52" s="9"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
       <c r="I52" s="9"/>
-      <c r="J52" s="10"/>
+      <c r="J52" s="12"/>
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
       <c r="M52" s="9"/>
       <c r="N52" s="9"/>
-      <c r="O52" s="10"/>
+      <c r="O52" s="12"/>
       <c r="P52" s="9"/>
-      <c r="Q52" s="11"/>
+      <c r="Q52" s="13"/>
       <c r="R52" s="9"/>
-      <c r="S52" s="10"/>
+      <c r="S52" s="12"/>
       <c r="T52" s="9"/>
-      <c r="U52" s="11"/>
+      <c r="U52" s="13"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="10"/>
+      <c r="W52" s="12"/>
       <c r="X52" s="9"/>
-      <c r="Y52" s="11"/>
+      <c r="Y52" s="13"/>
       <c r="Z52" s="9"/>
       <c r="AA52" s="9"/>
       <c r="AB52" s="9"/>
@@ -3028,31 +3224,31 @@
       <c r="AU52" s="9"/>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="9"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="11"/>
+      <c r="D53" s="13"/>
       <c r="E53" s="9"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
       <c r="I53" s="9"/>
-      <c r="J53" s="10"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
       <c r="N53" s="9"/>
-      <c r="O53" s="10"/>
+      <c r="O53" s="12"/>
       <c r="P53" s="9"/>
-      <c r="Q53" s="11"/>
+      <c r="Q53" s="13"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="10"/>
+      <c r="S53" s="12"/>
       <c r="T53" s="9"/>
-      <c r="U53" s="11"/>
+      <c r="U53" s="13"/>
       <c r="V53" s="9"/>
-      <c r="W53" s="10"/>
+      <c r="W53" s="12"/>
       <c r="X53" s="9"/>
-      <c r="Y53" s="11"/>
+      <c r="Y53" s="13"/>
       <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
       <c r="AB53" s="9"/>
@@ -3077,31 +3273,31 @@
       <c r="AU53" s="9"/>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="9"/>
+      <c r="A54" s="11"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="11"/>
+      <c r="D54" s="13"/>
       <c r="E54" s="9"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
       <c r="I54" s="9"/>
-      <c r="J54" s="10"/>
+      <c r="J54" s="12"/>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
-      <c r="O54" s="10"/>
+      <c r="O54" s="12"/>
       <c r="P54" s="9"/>
-      <c r="Q54" s="11"/>
+      <c r="Q54" s="13"/>
       <c r="R54" s="9"/>
-      <c r="S54" s="10"/>
+      <c r="S54" s="12"/>
       <c r="T54" s="9"/>
-      <c r="U54" s="11"/>
+      <c r="U54" s="13"/>
       <c r="V54" s="9"/>
-      <c r="W54" s="10"/>
+      <c r="W54" s="12"/>
       <c r="X54" s="9"/>
-      <c r="Y54" s="11"/>
+      <c r="Y54" s="13"/>
       <c r="Z54" s="9"/>
       <c r="AA54" s="9"/>
       <c r="AB54" s="9"/>
@@ -3126,31 +3322,31 @@
       <c r="AU54" s="9"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="9"/>
+      <c r="A55" s="11"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="11"/>
+      <c r="D55" s="13"/>
       <c r="E55" s="9"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
       <c r="I55" s="9"/>
-      <c r="J55" s="10"/>
+      <c r="J55" s="12"/>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
       <c r="N55" s="9"/>
-      <c r="O55" s="10"/>
+      <c r="O55" s="12"/>
       <c r="P55" s="9"/>
-      <c r="Q55" s="11"/>
+      <c r="Q55" s="13"/>
       <c r="R55" s="9"/>
-      <c r="S55" s="10"/>
+      <c r="S55" s="12"/>
       <c r="T55" s="9"/>
-      <c r="U55" s="11"/>
+      <c r="U55" s="13"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="10"/>
+      <c r="W55" s="12"/>
       <c r="X55" s="9"/>
-      <c r="Y55" s="11"/>
+      <c r="Y55" s="13"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
       <c r="AB55" s="9"/>
@@ -3175,31 +3371,31 @@
       <c r="AU55" s="9"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="9"/>
+      <c r="A56" s="11"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="11"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
       <c r="I56" s="9"/>
-      <c r="J56" s="10"/>
+      <c r="J56" s="12"/>
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
-      <c r="O56" s="10"/>
+      <c r="O56" s="12"/>
       <c r="P56" s="9"/>
-      <c r="Q56" s="11"/>
+      <c r="Q56" s="13"/>
       <c r="R56" s="9"/>
-      <c r="S56" s="10"/>
+      <c r="S56" s="12"/>
       <c r="T56" s="9"/>
-      <c r="U56" s="11"/>
+      <c r="U56" s="13"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="10"/>
+      <c r="W56" s="12"/>
       <c r="X56" s="9"/>
-      <c r="Y56" s="11"/>
+      <c r="Y56" s="13"/>
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
       <c r="AB56" s="9"/>
@@ -3224,31 +3420,31 @@
       <c r="AU56" s="9"/>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="9"/>
+      <c r="A57" s="11"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="11"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="9"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
       <c r="I57" s="9"/>
-      <c r="J57" s="10"/>
+      <c r="J57" s="12"/>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
-      <c r="O57" s="10"/>
+      <c r="O57" s="12"/>
       <c r="P57" s="9"/>
-      <c r="Q57" s="11"/>
+      <c r="Q57" s="13"/>
       <c r="R57" s="9"/>
-      <c r="S57" s="10"/>
+      <c r="S57" s="12"/>
       <c r="T57" s="9"/>
-      <c r="U57" s="11"/>
+      <c r="U57" s="13"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="10"/>
+      <c r="W57" s="12"/>
       <c r="X57" s="9"/>
-      <c r="Y57" s="11"/>
+      <c r="Y57" s="13"/>
       <c r="Z57" s="9"/>
       <c r="AA57" s="9"/>
       <c r="AB57" s="9"/>
@@ -3273,31 +3469,31 @@
       <c r="AU57" s="9"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="9"/>
+      <c r="A58" s="11"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
-      <c r="D58" s="11"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="9"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
       <c r="I58" s="9"/>
-      <c r="J58" s="10"/>
+      <c r="J58" s="12"/>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
-      <c r="O58" s="10"/>
+      <c r="O58" s="12"/>
       <c r="P58" s="9"/>
-      <c r="Q58" s="11"/>
+      <c r="Q58" s="13"/>
       <c r="R58" s="9"/>
-      <c r="S58" s="10"/>
+      <c r="S58" s="12"/>
       <c r="T58" s="9"/>
-      <c r="U58" s="11"/>
+      <c r="U58" s="13"/>
       <c r="V58" s="9"/>
-      <c r="W58" s="10"/>
+      <c r="W58" s="12"/>
       <c r="X58" s="9"/>
-      <c r="Y58" s="11"/>
+      <c r="Y58" s="13"/>
       <c r="Z58" s="9"/>
       <c r="AA58" s="9"/>
       <c r="AB58" s="9"/>
@@ -3322,31 +3518,31 @@
       <c r="AU58" s="9"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="9"/>
+      <c r="A59" s="11"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
-      <c r="D59" s="11"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="9"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
       <c r="I59" s="9"/>
-      <c r="J59" s="10"/>
+      <c r="J59" s="12"/>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="9"/>
       <c r="N59" s="9"/>
-      <c r="O59" s="10"/>
+      <c r="O59" s="12"/>
       <c r="P59" s="9"/>
-      <c r="Q59" s="11"/>
+      <c r="Q59" s="13"/>
       <c r="R59" s="9"/>
-      <c r="S59" s="10"/>
+      <c r="S59" s="12"/>
       <c r="T59" s="9"/>
-      <c r="U59" s="11"/>
+      <c r="U59" s="13"/>
       <c r="V59" s="9"/>
-      <c r="W59" s="10"/>
+      <c r="W59" s="12"/>
       <c r="X59" s="9"/>
-      <c r="Y59" s="11"/>
+      <c r="Y59" s="13"/>
       <c r="Z59" s="9"/>
       <c r="AA59" s="9"/>
       <c r="AB59" s="9"/>
@@ -3371,31 +3567,31 @@
       <c r="AU59" s="9"/>
     </row>
     <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="9"/>
+      <c r="A60" s="11"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
-      <c r="D60" s="11"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="9"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
       <c r="I60" s="9"/>
-      <c r="J60" s="10"/>
+      <c r="J60" s="12"/>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
-      <c r="O60" s="10"/>
+      <c r="O60" s="12"/>
       <c r="P60" s="9"/>
-      <c r="Q60" s="11"/>
+      <c r="Q60" s="13"/>
       <c r="R60" s="9"/>
-      <c r="S60" s="10"/>
+      <c r="S60" s="12"/>
       <c r="T60" s="9"/>
-      <c r="U60" s="11"/>
+      <c r="U60" s="13"/>
       <c r="V60" s="9"/>
-      <c r="W60" s="10"/>
+      <c r="W60" s="12"/>
       <c r="X60" s="9"/>
-      <c r="Y60" s="11"/>
+      <c r="Y60" s="13"/>
       <c r="Z60" s="9"/>
       <c r="AA60" s="9"/>
       <c r="AB60" s="9"/>
@@ -3420,31 +3616,31 @@
       <c r="AU60" s="9"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="9"/>
+      <c r="A61" s="11"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
-      <c r="D61" s="11"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="9"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
       <c r="I61" s="9"/>
-      <c r="J61" s="10"/>
+      <c r="J61" s="12"/>
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
-      <c r="O61" s="10"/>
+      <c r="O61" s="12"/>
       <c r="P61" s="9"/>
-      <c r="Q61" s="11"/>
+      <c r="Q61" s="13"/>
       <c r="R61" s="9"/>
-      <c r="S61" s="10"/>
+      <c r="S61" s="12"/>
       <c r="T61" s="9"/>
-      <c r="U61" s="11"/>
+      <c r="U61" s="13"/>
       <c r="V61" s="9"/>
-      <c r="W61" s="10"/>
+      <c r="W61" s="12"/>
       <c r="X61" s="9"/>
-      <c r="Y61" s="11"/>
+      <c r="Y61" s="13"/>
       <c r="Z61" s="9"/>
       <c r="AA61" s="9"/>
       <c r="AB61" s="9"/>
@@ -3469,31 +3665,31 @@
       <c r="AU61" s="9"/>
     </row>
     <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="9"/>
+      <c r="A62" s="11"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
-      <c r="D62" s="11"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="9"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
       <c r="I62" s="9"/>
-      <c r="J62" s="10"/>
+      <c r="J62" s="12"/>
       <c r="K62" s="9"/>
       <c r="L62" s="9"/>
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
-      <c r="O62" s="10"/>
+      <c r="O62" s="12"/>
       <c r="P62" s="9"/>
-      <c r="Q62" s="11"/>
+      <c r="Q62" s="13"/>
       <c r="R62" s="9"/>
-      <c r="S62" s="10"/>
+      <c r="S62" s="12"/>
       <c r="T62" s="9"/>
-      <c r="U62" s="11"/>
+      <c r="U62" s="13"/>
       <c r="V62" s="9"/>
-      <c r="W62" s="10"/>
+      <c r="W62" s="12"/>
       <c r="X62" s="9"/>
-      <c r="Y62" s="11"/>
+      <c r="Y62" s="13"/>
       <c r="Z62" s="9"/>
       <c r="AA62" s="9"/>
       <c r="AB62" s="9"/>
@@ -3518,31 +3714,31 @@
       <c r="AU62" s="9"/>
     </row>
     <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="9"/>
+      <c r="A63" s="11"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
-      <c r="D63" s="11"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="9"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
       <c r="I63" s="9"/>
-      <c r="J63" s="10"/>
+      <c r="J63" s="12"/>
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
       <c r="M63" s="9"/>
       <c r="N63" s="9"/>
-      <c r="O63" s="10"/>
+      <c r="O63" s="12"/>
       <c r="P63" s="9"/>
-      <c r="Q63" s="11"/>
+      <c r="Q63" s="13"/>
       <c r="R63" s="9"/>
-      <c r="S63" s="10"/>
+      <c r="S63" s="12"/>
       <c r="T63" s="9"/>
-      <c r="U63" s="11"/>
+      <c r="U63" s="13"/>
       <c r="V63" s="9"/>
-      <c r="W63" s="10"/>
+      <c r="W63" s="12"/>
       <c r="X63" s="9"/>
-      <c r="Y63" s="11"/>
+      <c r="Y63" s="13"/>
       <c r="Z63" s="9"/>
       <c r="AA63" s="9"/>
       <c r="AB63" s="9"/>
@@ -3567,31 +3763,31 @@
       <c r="AU63" s="9"/>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="9"/>
+      <c r="A64" s="11"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
-      <c r="D64" s="11"/>
+      <c r="D64" s="13"/>
       <c r="E64" s="9"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
       <c r="I64" s="9"/>
-      <c r="J64" s="10"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="9"/>
       <c r="L64" s="9"/>
       <c r="M64" s="9"/>
       <c r="N64" s="9"/>
-      <c r="O64" s="10"/>
+      <c r="O64" s="12"/>
       <c r="P64" s="9"/>
-      <c r="Q64" s="11"/>
+      <c r="Q64" s="13"/>
       <c r="R64" s="9"/>
-      <c r="S64" s="10"/>
+      <c r="S64" s="12"/>
       <c r="T64" s="9"/>
-      <c r="U64" s="11"/>
+      <c r="U64" s="13"/>
       <c r="V64" s="9"/>
-      <c r="W64" s="10"/>
+      <c r="W64" s="12"/>
       <c r="X64" s="9"/>
-      <c r="Y64" s="11"/>
+      <c r="Y64" s="13"/>
       <c r="Z64" s="9"/>
       <c r="AA64" s="9"/>
       <c r="AB64" s="9"/>
@@ -3616,31 +3812,31 @@
       <c r="AU64" s="9"/>
     </row>
     <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="9"/>
+      <c r="A65" s="11"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="13"/>
       <c r="E65" s="9"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
       <c r="I65" s="9"/>
-      <c r="J65" s="10"/>
+      <c r="J65" s="12"/>
       <c r="K65" s="9"/>
       <c r="L65" s="9"/>
       <c r="M65" s="9"/>
       <c r="N65" s="9"/>
-      <c r="O65" s="10"/>
+      <c r="O65" s="12"/>
       <c r="P65" s="9"/>
-      <c r="Q65" s="11"/>
+      <c r="Q65" s="13"/>
       <c r="R65" s="9"/>
-      <c r="S65" s="10"/>
+      <c r="S65" s="12"/>
       <c r="T65" s="9"/>
-      <c r="U65" s="11"/>
+      <c r="U65" s="13"/>
       <c r="V65" s="9"/>
-      <c r="W65" s="10"/>
+      <c r="W65" s="12"/>
       <c r="X65" s="9"/>
-      <c r="Y65" s="11"/>
+      <c r="Y65" s="13"/>
       <c r="Z65" s="9"/>
       <c r="AA65" s="9"/>
       <c r="AB65" s="9"/>
@@ -3665,31 +3861,31 @@
       <c r="AU65" s="9"/>
     </row>
     <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="9"/>
+      <c r="A66" s="11"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
-      <c r="D66" s="11"/>
+      <c r="D66" s="13"/>
       <c r="E66" s="9"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
       <c r="I66" s="9"/>
-      <c r="J66" s="10"/>
+      <c r="J66" s="12"/>
       <c r="K66" s="9"/>
       <c r="L66" s="9"/>
       <c r="M66" s="9"/>
       <c r="N66" s="9"/>
-      <c r="O66" s="10"/>
+      <c r="O66" s="12"/>
       <c r="P66" s="9"/>
-      <c r="Q66" s="11"/>
+      <c r="Q66" s="13"/>
       <c r="R66" s="9"/>
-      <c r="S66" s="10"/>
+      <c r="S66" s="12"/>
       <c r="T66" s="9"/>
-      <c r="U66" s="11"/>
+      <c r="U66" s="13"/>
       <c r="V66" s="9"/>
-      <c r="W66" s="10"/>
+      <c r="W66" s="12"/>
       <c r="X66" s="9"/>
-      <c r="Y66" s="11"/>
+      <c r="Y66" s="13"/>
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="9"/>
@@ -3714,31 +3910,31 @@
       <c r="AU66" s="9"/>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="9"/>
+      <c r="A67" s="11"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="11"/>
+      <c r="D67" s="13"/>
       <c r="E67" s="9"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
       <c r="I67" s="9"/>
-      <c r="J67" s="10"/>
+      <c r="J67" s="12"/>
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
       <c r="M67" s="9"/>
       <c r="N67" s="9"/>
-      <c r="O67" s="10"/>
+      <c r="O67" s="12"/>
       <c r="P67" s="9"/>
-      <c r="Q67" s="11"/>
+      <c r="Q67" s="13"/>
       <c r="R67" s="9"/>
-      <c r="S67" s="10"/>
+      <c r="S67" s="12"/>
       <c r="T67" s="9"/>
-      <c r="U67" s="11"/>
+      <c r="U67" s="13"/>
       <c r="V67" s="9"/>
-      <c r="W67" s="10"/>
+      <c r="W67" s="12"/>
       <c r="X67" s="9"/>
-      <c r="Y67" s="11"/>
+      <c r="Y67" s="13"/>
       <c r="Z67" s="9"/>
       <c r="AA67" s="9"/>
       <c r="AB67" s="9"/>
@@ -3763,31 +3959,31 @@
       <c r="AU67" s="9"/>
     </row>
     <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="9"/>
+      <c r="A68" s="11"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
-      <c r="D68" s="11"/>
+      <c r="D68" s="13"/>
       <c r="E68" s="9"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
       <c r="I68" s="9"/>
-      <c r="J68" s="10"/>
+      <c r="J68" s="12"/>
       <c r="K68" s="9"/>
       <c r="L68" s="9"/>
       <c r="M68" s="9"/>
       <c r="N68" s="9"/>
-      <c r="O68" s="10"/>
+      <c r="O68" s="12"/>
       <c r="P68" s="9"/>
-      <c r="Q68" s="11"/>
+      <c r="Q68" s="13"/>
       <c r="R68" s="9"/>
-      <c r="S68" s="10"/>
+      <c r="S68" s="12"/>
       <c r="T68" s="9"/>
-      <c r="U68" s="11"/>
+      <c r="U68" s="13"/>
       <c r="V68" s="9"/>
-      <c r="W68" s="10"/>
+      <c r="W68" s="12"/>
       <c r="X68" s="9"/>
-      <c r="Y68" s="11"/>
+      <c r="Y68" s="13"/>
       <c r="Z68" s="9"/>
       <c r="AA68" s="9"/>
       <c r="AB68" s="9"/>
@@ -3812,31 +4008,31 @@
       <c r="AU68" s="9"/>
     </row>
     <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="9"/>
+      <c r="A69" s="11"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
-      <c r="D69" s="11"/>
+      <c r="D69" s="13"/>
       <c r="E69" s="9"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
       <c r="I69" s="9"/>
-      <c r="J69" s="10"/>
+      <c r="J69" s="12"/>
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
       <c r="M69" s="9"/>
       <c r="N69" s="9"/>
-      <c r="O69" s="10"/>
+      <c r="O69" s="12"/>
       <c r="P69" s="9"/>
-      <c r="Q69" s="11"/>
+      <c r="Q69" s="13"/>
       <c r="R69" s="9"/>
-      <c r="S69" s="10"/>
+      <c r="S69" s="12"/>
       <c r="T69" s="9"/>
-      <c r="U69" s="11"/>
+      <c r="U69" s="13"/>
       <c r="V69" s="9"/>
-      <c r="W69" s="10"/>
+      <c r="W69" s="12"/>
       <c r="X69" s="9"/>
-      <c r="Y69" s="11"/>
+      <c r="Y69" s="13"/>
       <c r="Z69" s="9"/>
       <c r="AA69" s="9"/>
       <c r="AB69" s="9"/>
@@ -3861,31 +4057,31 @@
       <c r="AU69" s="9"/>
     </row>
     <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="9"/>
+      <c r="A70" s="11"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
-      <c r="D70" s="11"/>
+      <c r="D70" s="13"/>
       <c r="E70" s="9"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
       <c r="I70" s="9"/>
-      <c r="J70" s="10"/>
+      <c r="J70" s="12"/>
       <c r="K70" s="9"/>
       <c r="L70" s="9"/>
       <c r="M70" s="9"/>
       <c r="N70" s="9"/>
-      <c r="O70" s="10"/>
+      <c r="O70" s="12"/>
       <c r="P70" s="9"/>
-      <c r="Q70" s="11"/>
+      <c r="Q70" s="13"/>
       <c r="R70" s="9"/>
-      <c r="S70" s="10"/>
+      <c r="S70" s="12"/>
       <c r="T70" s="9"/>
-      <c r="U70" s="11"/>
+      <c r="U70" s="13"/>
       <c r="V70" s="9"/>
-      <c r="W70" s="10"/>
+      <c r="W70" s="12"/>
       <c r="X70" s="9"/>
-      <c r="Y70" s="11"/>
+      <c r="Y70" s="13"/>
       <c r="Z70" s="9"/>
       <c r="AA70" s="9"/>
       <c r="AB70" s="9"/>
@@ -3910,31 +4106,31 @@
       <c r="AU70" s="9"/>
     </row>
     <row r="71" ht="32" customHeight="1">
-      <c r="A71" s="9"/>
+      <c r="A71" s="11"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
-      <c r="D71" s="11"/>
+      <c r="D71" s="13"/>
       <c r="E71" s="9"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="10"/>
+      <c r="J71" s="12"/>
       <c r="K71" s="9"/>
       <c r="L71" s="9"/>
       <c r="M71" s="9"/>
       <c r="N71" s="9"/>
-      <c r="O71" s="10"/>
+      <c r="O71" s="12"/>
       <c r="P71" s="9"/>
-      <c r="Q71" s="11"/>
+      <c r="Q71" s="13"/>
       <c r="R71" s="9"/>
-      <c r="S71" s="10"/>
+      <c r="S71" s="12"/>
       <c r="T71" s="9"/>
-      <c r="U71" s="11"/>
+      <c r="U71" s="13"/>
       <c r="V71" s="9"/>
-      <c r="W71" s="10"/>
+      <c r="W71" s="12"/>
       <c r="X71" s="9"/>
-      <c r="Y71" s="11"/>
+      <c r="Y71" s="13"/>
       <c r="Z71" s="9"/>
       <c r="AA71" s="9"/>
       <c r="AB71" s="9"/>
@@ -3959,31 +4155,31 @@
       <c r="AU71" s="9"/>
     </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="9"/>
+      <c r="A72" s="11"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="13"/>
       <c r="E72" s="9"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
       <c r="I72" s="9"/>
-      <c r="J72" s="10"/>
+      <c r="J72" s="12"/>
       <c r="K72" s="9"/>
       <c r="L72" s="9"/>
       <c r="M72" s="9"/>
       <c r="N72" s="9"/>
-      <c r="O72" s="10"/>
+      <c r="O72" s="12"/>
       <c r="P72" s="9"/>
-      <c r="Q72" s="11"/>
+      <c r="Q72" s="13"/>
       <c r="R72" s="9"/>
-      <c r="S72" s="10"/>
+      <c r="S72" s="12"/>
       <c r="T72" s="9"/>
-      <c r="U72" s="11"/>
+      <c r="U72" s="13"/>
       <c r="V72" s="9"/>
-      <c r="W72" s="10"/>
+      <c r="W72" s="12"/>
       <c r="X72" s="9"/>
-      <c r="Y72" s="11"/>
+      <c r="Y72" s="13"/>
       <c r="Z72" s="9"/>
       <c r="AA72" s="9"/>
       <c r="AB72" s="9"/>
@@ -4008,31 +4204,31 @@
       <c r="AU72" s="9"/>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="9"/>
+      <c r="A73" s="11"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
-      <c r="D73" s="11"/>
+      <c r="D73" s="13"/>
       <c r="E73" s="9"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
       <c r="I73" s="9"/>
-      <c r="J73" s="10"/>
+      <c r="J73" s="12"/>
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
       <c r="M73" s="9"/>
       <c r="N73" s="9"/>
-      <c r="O73" s="10"/>
+      <c r="O73" s="12"/>
       <c r="P73" s="9"/>
-      <c r="Q73" s="11"/>
+      <c r="Q73" s="13"/>
       <c r="R73" s="9"/>
-      <c r="S73" s="10"/>
+      <c r="S73" s="12"/>
       <c r="T73" s="9"/>
-      <c r="U73" s="11"/>
+      <c r="U73" s="13"/>
       <c r="V73" s="9"/>
-      <c r="W73" s="10"/>
+      <c r="W73" s="12"/>
       <c r="X73" s="9"/>
-      <c r="Y73" s="11"/>
+      <c r="Y73" s="13"/>
       <c r="Z73" s="9"/>
       <c r="AA73" s="9"/>
       <c r="AB73" s="9"/>
@@ -4057,31 +4253,31 @@
       <c r="AU73" s="9"/>
     </row>
     <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="9"/>
+      <c r="A74" s="11"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
-      <c r="D74" s="11"/>
+      <c r="D74" s="13"/>
       <c r="E74" s="9"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
       <c r="I74" s="9"/>
-      <c r="J74" s="10"/>
+      <c r="J74" s="12"/>
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
       <c r="M74" s="9"/>
       <c r="N74" s="9"/>
-      <c r="O74" s="10"/>
+      <c r="O74" s="12"/>
       <c r="P74" s="9"/>
-      <c r="Q74" s="11"/>
+      <c r="Q74" s="13"/>
       <c r="R74" s="9"/>
-      <c r="S74" s="10"/>
+      <c r="S74" s="12"/>
       <c r="T74" s="9"/>
-      <c r="U74" s="11"/>
+      <c r="U74" s="13"/>
       <c r="V74" s="9"/>
-      <c r="W74" s="10"/>
+      <c r="W74" s="12"/>
       <c r="X74" s="9"/>
-      <c r="Y74" s="11"/>
+      <c r="Y74" s="13"/>
       <c r="Z74" s="9"/>
       <c r="AA74" s="9"/>
       <c r="AB74" s="9"/>
@@ -4106,31 +4302,31 @@
       <c r="AU74" s="9"/>
     </row>
     <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="9"/>
+      <c r="A75" s="11"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
-      <c r="D75" s="11"/>
+      <c r="D75" s="13"/>
       <c r="E75" s="9"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
       <c r="I75" s="9"/>
-      <c r="J75" s="10"/>
+      <c r="J75" s="12"/>
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
       <c r="M75" s="9"/>
       <c r="N75" s="9"/>
-      <c r="O75" s="10"/>
+      <c r="O75" s="12"/>
       <c r="P75" s="9"/>
-      <c r="Q75" s="11"/>
+      <c r="Q75" s="13"/>
       <c r="R75" s="9"/>
-      <c r="S75" s="10"/>
+      <c r="S75" s="12"/>
       <c r="T75" s="9"/>
-      <c r="U75" s="11"/>
+      <c r="U75" s="13"/>
       <c r="V75" s="9"/>
-      <c r="W75" s="10"/>
+      <c r="W75" s="12"/>
       <c r="X75" s="9"/>
-      <c r="Y75" s="11"/>
+      <c r="Y75" s="13"/>
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="9"/>
@@ -4155,31 +4351,31 @@
       <c r="AU75" s="9"/>
     </row>
     <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="9"/>
+      <c r="A76" s="11"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
-      <c r="D76" s="11"/>
+      <c r="D76" s="13"/>
       <c r="E76" s="9"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
       <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
+      <c r="J76" s="12"/>
       <c r="K76" s="9"/>
       <c r="L76" s="9"/>
       <c r="M76" s="9"/>
       <c r="N76" s="9"/>
-      <c r="O76" s="10"/>
+      <c r="O76" s="12"/>
       <c r="P76" s="9"/>
-      <c r="Q76" s="11"/>
+      <c r="Q76" s="13"/>
       <c r="R76" s="9"/>
-      <c r="S76" s="10"/>
+      <c r="S76" s="12"/>
       <c r="T76" s="9"/>
-      <c r="U76" s="11"/>
+      <c r="U76" s="13"/>
       <c r="V76" s="9"/>
-      <c r="W76" s="10"/>
+      <c r="W76" s="12"/>
       <c r="X76" s="9"/>
-      <c r="Y76" s="11"/>
+      <c r="Y76" s="13"/>
       <c r="Z76" s="9"/>
       <c r="AA76" s="9"/>
       <c r="AB76" s="9"/>
@@ -4204,31 +4400,31 @@
       <c r="AU76" s="9"/>
     </row>
     <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="9"/>
+      <c r="A77" s="11"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
-      <c r="D77" s="11"/>
+      <c r="D77" s="13"/>
       <c r="E77" s="9"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
       <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
+      <c r="J77" s="12"/>
       <c r="K77" s="9"/>
       <c r="L77" s="9"/>
       <c r="M77" s="9"/>
       <c r="N77" s="9"/>
-      <c r="O77" s="10"/>
+      <c r="O77" s="12"/>
       <c r="P77" s="9"/>
-      <c r="Q77" s="11"/>
+      <c r="Q77" s="13"/>
       <c r="R77" s="9"/>
-      <c r="S77" s="10"/>
+      <c r="S77" s="12"/>
       <c r="T77" s="9"/>
-      <c r="U77" s="11"/>
+      <c r="U77" s="13"/>
       <c r="V77" s="9"/>
-      <c r="W77" s="10"/>
+      <c r="W77" s="12"/>
       <c r="X77" s="9"/>
-      <c r="Y77" s="11"/>
+      <c r="Y77" s="13"/>
       <c r="Z77" s="9"/>
       <c r="AA77" s="9"/>
       <c r="AB77" s="9"/>
@@ -4253,31 +4449,31 @@
       <c r="AU77" s="9"/>
     </row>
     <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="9"/>
+      <c r="A78" s="11"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
-      <c r="D78" s="11"/>
+      <c r="D78" s="13"/>
       <c r="E78" s="9"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
       <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
+      <c r="J78" s="12"/>
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
       <c r="M78" s="9"/>
       <c r="N78" s="9"/>
-      <c r="O78" s="10"/>
+      <c r="O78" s="12"/>
       <c r="P78" s="9"/>
-      <c r="Q78" s="11"/>
+      <c r="Q78" s="13"/>
       <c r="R78" s="9"/>
-      <c r="S78" s="10"/>
+      <c r="S78" s="12"/>
       <c r="T78" s="9"/>
-      <c r="U78" s="11"/>
+      <c r="U78" s="13"/>
       <c r="V78" s="9"/>
-      <c r="W78" s="10"/>
+      <c r="W78" s="12"/>
       <c r="X78" s="9"/>
-      <c r="Y78" s="11"/>
+      <c r="Y78" s="13"/>
       <c r="Z78" s="9"/>
       <c r="AA78" s="9"/>
       <c r="AB78" s="9"/>
@@ -4302,31 +4498,31 @@
       <c r="AU78" s="9"/>
     </row>
     <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="9"/>
+      <c r="A79" s="11"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
-      <c r="D79" s="11"/>
+      <c r="D79" s="13"/>
       <c r="E79" s="9"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
       <c r="I79" s="9"/>
-      <c r="J79" s="10"/>
+      <c r="J79" s="12"/>
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
       <c r="M79" s="9"/>
       <c r="N79" s="9"/>
-      <c r="O79" s="10"/>
+      <c r="O79" s="12"/>
       <c r="P79" s="9"/>
-      <c r="Q79" s="11"/>
+      <c r="Q79" s="13"/>
       <c r="R79" s="9"/>
-      <c r="S79" s="10"/>
+      <c r="S79" s="12"/>
       <c r="T79" s="9"/>
-      <c r="U79" s="11"/>
+      <c r="U79" s="13"/>
       <c r="V79" s="9"/>
-      <c r="W79" s="10"/>
+      <c r="W79" s="12"/>
       <c r="X79" s="9"/>
-      <c r="Y79" s="11"/>
+      <c r="Y79" s="13"/>
       <c r="Z79" s="9"/>
       <c r="AA79" s="9"/>
       <c r="AB79" s="9"/>
@@ -4351,31 +4547,31 @@
       <c r="AU79" s="9"/>
     </row>
     <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="9"/>
+      <c r="A80" s="11"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
-      <c r="D80" s="11"/>
+      <c r="D80" s="13"/>
       <c r="E80" s="9"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
       <c r="I80" s="9"/>
-      <c r="J80" s="10"/>
+      <c r="J80" s="12"/>
       <c r="K80" s="9"/>
       <c r="L80" s="9"/>
       <c r="M80" s="9"/>
       <c r="N80" s="9"/>
-      <c r="O80" s="10"/>
+      <c r="O80" s="12"/>
       <c r="P80" s="9"/>
-      <c r="Q80" s="11"/>
+      <c r="Q80" s="13"/>
       <c r="R80" s="9"/>
-      <c r="S80" s="10"/>
+      <c r="S80" s="12"/>
       <c r="T80" s="9"/>
-      <c r="U80" s="11"/>
+      <c r="U80" s="13"/>
       <c r="V80" s="9"/>
-      <c r="W80" s="10"/>
+      <c r="W80" s="12"/>
       <c r="X80" s="9"/>
-      <c r="Y80" s="11"/>
+      <c r="Y80" s="13"/>
       <c r="Z80" s="9"/>
       <c r="AA80" s="9"/>
       <c r="AB80" s="9"/>
@@ -4400,31 +4596,31 @@
       <c r="AU80" s="9"/>
     </row>
     <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="9"/>
+      <c r="A81" s="11"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
-      <c r="D81" s="11"/>
+      <c r="D81" s="13"/>
       <c r="E81" s="9"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
       <c r="I81" s="9"/>
-      <c r="J81" s="10"/>
+      <c r="J81" s="12"/>
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
       <c r="M81" s="9"/>
       <c r="N81" s="9"/>
-      <c r="O81" s="10"/>
+      <c r="O81" s="12"/>
       <c r="P81" s="9"/>
-      <c r="Q81" s="11"/>
+      <c r="Q81" s="13"/>
       <c r="R81" s="9"/>
-      <c r="S81" s="10"/>
+      <c r="S81" s="12"/>
       <c r="T81" s="9"/>
-      <c r="U81" s="11"/>
+      <c r="U81" s="13"/>
       <c r="V81" s="9"/>
-      <c r="W81" s="10"/>
+      <c r="W81" s="12"/>
       <c r="X81" s="9"/>
-      <c r="Y81" s="11"/>
+      <c r="Y81" s="13"/>
       <c r="Z81" s="9"/>
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
@@ -4449,31 +4645,31 @@
       <c r="AU81" s="9"/>
     </row>
     <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="9"/>
+      <c r="A82" s="11"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
-      <c r="D82" s="11"/>
+      <c r="D82" s="13"/>
       <c r="E82" s="9"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
       <c r="I82" s="9"/>
-      <c r="J82" s="10"/>
+      <c r="J82" s="12"/>
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
       <c r="M82" s="9"/>
       <c r="N82" s="9"/>
-      <c r="O82" s="10"/>
+      <c r="O82" s="12"/>
       <c r="P82" s="9"/>
-      <c r="Q82" s="11"/>
+      <c r="Q82" s="13"/>
       <c r="R82" s="9"/>
-      <c r="S82" s="10"/>
+      <c r="S82" s="12"/>
       <c r="T82" s="9"/>
-      <c r="U82" s="11"/>
+      <c r="U82" s="13"/>
       <c r="V82" s="9"/>
-      <c r="W82" s="10"/>
+      <c r="W82" s="12"/>
       <c r="X82" s="9"/>
-      <c r="Y82" s="11"/>
+      <c r="Y82" s="13"/>
       <c r="Z82" s="9"/>
       <c r="AA82" s="9"/>
       <c r="AB82" s="9"/>
@@ -4498,31 +4694,31 @@
       <c r="AU82" s="9"/>
     </row>
     <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="9"/>
+      <c r="A83" s="11"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
-      <c r="D83" s="11"/>
+      <c r="D83" s="13"/>
       <c r="E83" s="9"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
       <c r="I83" s="9"/>
-      <c r="J83" s="10"/>
+      <c r="J83" s="12"/>
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
       <c r="M83" s="9"/>
       <c r="N83" s="9"/>
-      <c r="O83" s="10"/>
+      <c r="O83" s="12"/>
       <c r="P83" s="9"/>
-      <c r="Q83" s="11"/>
+      <c r="Q83" s="13"/>
       <c r="R83" s="9"/>
-      <c r="S83" s="10"/>
+      <c r="S83" s="12"/>
       <c r="T83" s="9"/>
-      <c r="U83" s="11"/>
+      <c r="U83" s="13"/>
       <c r="V83" s="9"/>
-      <c r="W83" s="10"/>
+      <c r="W83" s="12"/>
       <c r="X83" s="9"/>
-      <c r="Y83" s="11"/>
+      <c r="Y83" s="13"/>
       <c r="Z83" s="9"/>
       <c r="AA83" s="9"/>
       <c r="AB83" s="9"/>
@@ -4547,31 +4743,31 @@
       <c r="AU83" s="9"/>
     </row>
     <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="9"/>
+      <c r="A84" s="11"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
-      <c r="D84" s="11"/>
+      <c r="D84" s="13"/>
       <c r="E84" s="9"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
       <c r="I84" s="9"/>
-      <c r="J84" s="10"/>
+      <c r="J84" s="12"/>
       <c r="K84" s="9"/>
       <c r="L84" s="9"/>
       <c r="M84" s="9"/>
       <c r="N84" s="9"/>
-      <c r="O84" s="10"/>
+      <c r="O84" s="12"/>
       <c r="P84" s="9"/>
-      <c r="Q84" s="11"/>
+      <c r="Q84" s="13"/>
       <c r="R84" s="9"/>
-      <c r="S84" s="10"/>
+      <c r="S84" s="12"/>
       <c r="T84" s="9"/>
-      <c r="U84" s="11"/>
+      <c r="U84" s="13"/>
       <c r="V84" s="9"/>
-      <c r="W84" s="10"/>
+      <c r="W84" s="12"/>
       <c r="X84" s="9"/>
-      <c r="Y84" s="11"/>
+      <c r="Y84" s="13"/>
       <c r="Z84" s="9"/>
       <c r="AA84" s="9"/>
       <c r="AB84" s="9"/>
@@ -4596,31 +4792,31 @@
       <c r="AU84" s="9"/>
     </row>
     <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="9"/>
+      <c r="A85" s="11"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
-      <c r="D85" s="11"/>
+      <c r="D85" s="13"/>
       <c r="E85" s="9"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
       <c r="I85" s="9"/>
-      <c r="J85" s="10"/>
+      <c r="J85" s="12"/>
       <c r="K85" s="9"/>
       <c r="L85" s="9"/>
       <c r="M85" s="9"/>
       <c r="N85" s="9"/>
-      <c r="O85" s="10"/>
+      <c r="O85" s="12"/>
       <c r="P85" s="9"/>
-      <c r="Q85" s="11"/>
+      <c r="Q85" s="13"/>
       <c r="R85" s="9"/>
-      <c r="S85" s="10"/>
+      <c r="S85" s="12"/>
       <c r="T85" s="9"/>
-      <c r="U85" s="11"/>
+      <c r="U85" s="13"/>
       <c r="V85" s="9"/>
-      <c r="W85" s="10"/>
+      <c r="W85" s="12"/>
       <c r="X85" s="9"/>
-      <c r="Y85" s="11"/>
+      <c r="Y85" s="13"/>
       <c r="Z85" s="9"/>
       <c r="AA85" s="9"/>
       <c r="AB85" s="9"/>
@@ -4645,31 +4841,31 @@
       <c r="AU85" s="9"/>
     </row>
     <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="9"/>
+      <c r="A86" s="11"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
-      <c r="D86" s="11"/>
+      <c r="D86" s="13"/>
       <c r="E86" s="9"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
       <c r="I86" s="9"/>
-      <c r="J86" s="10"/>
+      <c r="J86" s="12"/>
       <c r="K86" s="9"/>
       <c r="L86" s="9"/>
       <c r="M86" s="9"/>
       <c r="N86" s="9"/>
-      <c r="O86" s="10"/>
+      <c r="O86" s="12"/>
       <c r="P86" s="9"/>
-      <c r="Q86" s="11"/>
+      <c r="Q86" s="13"/>
       <c r="R86" s="9"/>
-      <c r="S86" s="10"/>
+      <c r="S86" s="12"/>
       <c r="T86" s="9"/>
-      <c r="U86" s="11"/>
+      <c r="U86" s="13"/>
       <c r="V86" s="9"/>
-      <c r="W86" s="10"/>
+      <c r="W86" s="12"/>
       <c r="X86" s="9"/>
-      <c r="Y86" s="11"/>
+      <c r="Y86" s="13"/>
       <c r="Z86" s="9"/>
       <c r="AA86" s="9"/>
       <c r="AB86" s="9"/>
@@ -4694,31 +4890,31 @@
       <c r="AU86" s="9"/>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="9"/>
+      <c r="A87" s="11"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
-      <c r="D87" s="11"/>
+      <c r="D87" s="13"/>
       <c r="E87" s="9"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
       <c r="I87" s="9"/>
-      <c r="J87" s="10"/>
+      <c r="J87" s="12"/>
       <c r="K87" s="9"/>
       <c r="L87" s="9"/>
       <c r="M87" s="9"/>
       <c r="N87" s="9"/>
-      <c r="O87" s="10"/>
+      <c r="O87" s="12"/>
       <c r="P87" s="9"/>
-      <c r="Q87" s="11"/>
+      <c r="Q87" s="13"/>
       <c r="R87" s="9"/>
-      <c r="S87" s="10"/>
+      <c r="S87" s="12"/>
       <c r="T87" s="9"/>
-      <c r="U87" s="11"/>
+      <c r="U87" s="13"/>
       <c r="V87" s="9"/>
-      <c r="W87" s="10"/>
+      <c r="W87" s="12"/>
       <c r="X87" s="9"/>
-      <c r="Y87" s="11"/>
+      <c r="Y87" s="13"/>
       <c r="Z87" s="9"/>
       <c r="AA87" s="9"/>
       <c r="AB87" s="9"/>
@@ -4743,31 +4939,31 @@
       <c r="AU87" s="9"/>
     </row>
     <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="9"/>
+      <c r="A88" s="11"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
-      <c r="D88" s="11"/>
+      <c r="D88" s="13"/>
       <c r="E88" s="9"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
       <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
+      <c r="J88" s="12"/>
       <c r="K88" s="9"/>
       <c r="L88" s="9"/>
       <c r="M88" s="9"/>
       <c r="N88" s="9"/>
-      <c r="O88" s="10"/>
+      <c r="O88" s="12"/>
       <c r="P88" s="9"/>
-      <c r="Q88" s="11"/>
+      <c r="Q88" s="13"/>
       <c r="R88" s="9"/>
-      <c r="S88" s="10"/>
+      <c r="S88" s="12"/>
       <c r="T88" s="9"/>
-      <c r="U88" s="11"/>
+      <c r="U88" s="13"/>
       <c r="V88" s="9"/>
-      <c r="W88" s="10"/>
+      <c r="W88" s="12"/>
       <c r="X88" s="9"/>
-      <c r="Y88" s="11"/>
+      <c r="Y88" s="13"/>
       <c r="Z88" s="9"/>
       <c r="AA88" s="9"/>
       <c r="AB88" s="9"/>
@@ -4792,31 +4988,31 @@
       <c r="AU88" s="9"/>
     </row>
     <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="9"/>
+      <c r="A89" s="11"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
-      <c r="D89" s="11"/>
+      <c r="D89" s="13"/>
       <c r="E89" s="9"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
       <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
+      <c r="J89" s="12"/>
       <c r="K89" s="9"/>
       <c r="L89" s="9"/>
       <c r="M89" s="9"/>
       <c r="N89" s="9"/>
-      <c r="O89" s="10"/>
+      <c r="O89" s="12"/>
       <c r="P89" s="9"/>
-      <c r="Q89" s="11"/>
+      <c r="Q89" s="13"/>
       <c r="R89" s="9"/>
-      <c r="S89" s="10"/>
+      <c r="S89" s="12"/>
       <c r="T89" s="9"/>
-      <c r="U89" s="11"/>
+      <c r="U89" s="13"/>
       <c r="V89" s="9"/>
-      <c r="W89" s="10"/>
+      <c r="W89" s="12"/>
       <c r="X89" s="9"/>
-      <c r="Y89" s="11"/>
+      <c r="Y89" s="13"/>
       <c r="Z89" s="9"/>
       <c r="AA89" s="9"/>
       <c r="AB89" s="9"/>
@@ -4841,31 +5037,31 @@
       <c r="AU89" s="9"/>
     </row>
     <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="9"/>
+      <c r="A90" s="11"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
-      <c r="D90" s="11"/>
+      <c r="D90" s="13"/>
       <c r="E90" s="9"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
       <c r="I90" s="9"/>
-      <c r="J90" s="10"/>
+      <c r="J90" s="12"/>
       <c r="K90" s="9"/>
       <c r="L90" s="9"/>
       <c r="M90" s="9"/>
       <c r="N90" s="9"/>
-      <c r="O90" s="10"/>
+      <c r="O90" s="12"/>
       <c r="P90" s="9"/>
-      <c r="Q90" s="11"/>
+      <c r="Q90" s="13"/>
       <c r="R90" s="9"/>
-      <c r="S90" s="10"/>
+      <c r="S90" s="12"/>
       <c r="T90" s="9"/>
-      <c r="U90" s="11"/>
+      <c r="U90" s="13"/>
       <c r="V90" s="9"/>
-      <c r="W90" s="10"/>
+      <c r="W90" s="12"/>
       <c r="X90" s="9"/>
-      <c r="Y90" s="11"/>
+      <c r="Y90" s="13"/>
       <c r="Z90" s="9"/>
       <c r="AA90" s="9"/>
       <c r="AB90" s="9"/>
@@ -4890,31 +5086,31 @@
       <c r="AU90" s="9"/>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="9"/>
+      <c r="A91" s="11"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
-      <c r="D91" s="11"/>
+      <c r="D91" s="13"/>
       <c r="E91" s="9"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
       <c r="I91" s="9"/>
-      <c r="J91" s="10"/>
+      <c r="J91" s="12"/>
       <c r="K91" s="9"/>
       <c r="L91" s="9"/>
       <c r="M91" s="9"/>
       <c r="N91" s="9"/>
-      <c r="O91" s="10"/>
+      <c r="O91" s="12"/>
       <c r="P91" s="9"/>
-      <c r="Q91" s="11"/>
+      <c r="Q91" s="13"/>
       <c r="R91" s="9"/>
-      <c r="S91" s="10"/>
+      <c r="S91" s="12"/>
       <c r="T91" s="9"/>
-      <c r="U91" s="11"/>
+      <c r="U91" s="13"/>
       <c r="V91" s="9"/>
-      <c r="W91" s="10"/>
+      <c r="W91" s="12"/>
       <c r="X91" s="9"/>
-      <c r="Y91" s="11"/>
+      <c r="Y91" s="13"/>
       <c r="Z91" s="9"/>
       <c r="AA91" s="9"/>
       <c r="AB91" s="9"/>
@@ -4939,31 +5135,31 @@
       <c r="AU91" s="9"/>
     </row>
     <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="9"/>
+      <c r="A92" s="11"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
-      <c r="D92" s="11"/>
+      <c r="D92" s="13"/>
       <c r="E92" s="9"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
       <c r="I92" s="9"/>
-      <c r="J92" s="10"/>
+      <c r="J92" s="12"/>
       <c r="K92" s="9"/>
       <c r="L92" s="9"/>
       <c r="M92" s="9"/>
       <c r="N92" s="9"/>
-      <c r="O92" s="10"/>
+      <c r="O92" s="12"/>
       <c r="P92" s="9"/>
-      <c r="Q92" s="11"/>
+      <c r="Q92" s="13"/>
       <c r="R92" s="9"/>
-      <c r="S92" s="10"/>
+      <c r="S92" s="12"/>
       <c r="T92" s="9"/>
-      <c r="U92" s="11"/>
+      <c r="U92" s="13"/>
       <c r="V92" s="9"/>
-      <c r="W92" s="10"/>
+      <c r="W92" s="12"/>
       <c r="X92" s="9"/>
-      <c r="Y92" s="11"/>
+      <c r="Y92" s="13"/>
       <c r="Z92" s="9"/>
       <c r="AA92" s="9"/>
       <c r="AB92" s="9"/>
@@ -4988,31 +5184,31 @@
       <c r="AU92" s="9"/>
     </row>
     <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="9"/>
+      <c r="A93" s="11"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
-      <c r="D93" s="11"/>
+      <c r="D93" s="13"/>
       <c r="E93" s="9"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
       <c r="I93" s="9"/>
-      <c r="J93" s="10"/>
+      <c r="J93" s="12"/>
       <c r="K93" s="9"/>
       <c r="L93" s="9"/>
       <c r="M93" s="9"/>
       <c r="N93" s="9"/>
-      <c r="O93" s="10"/>
+      <c r="O93" s="12"/>
       <c r="P93" s="9"/>
-      <c r="Q93" s="11"/>
+      <c r="Q93" s="13"/>
       <c r="R93" s="9"/>
-      <c r="S93" s="10"/>
+      <c r="S93" s="12"/>
       <c r="T93" s="9"/>
-      <c r="U93" s="11"/>
+      <c r="U93" s="13"/>
       <c r="V93" s="9"/>
-      <c r="W93" s="10"/>
+      <c r="W93" s="12"/>
       <c r="X93" s="9"/>
-      <c r="Y93" s="11"/>
+      <c r="Y93" s="13"/>
       <c r="Z93" s="9"/>
       <c r="AA93" s="9"/>
       <c r="AB93" s="9"/>
@@ -5037,31 +5233,31 @@
       <c r="AU93" s="9"/>
     </row>
     <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="9"/>
+      <c r="A94" s="11"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
-      <c r="D94" s="11"/>
+      <c r="D94" s="13"/>
       <c r="E94" s="9"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
       <c r="I94" s="9"/>
-      <c r="J94" s="10"/>
+      <c r="J94" s="12"/>
       <c r="K94" s="9"/>
       <c r="L94" s="9"/>
       <c r="M94" s="9"/>
       <c r="N94" s="9"/>
-      <c r="O94" s="10"/>
+      <c r="O94" s="12"/>
       <c r="P94" s="9"/>
-      <c r="Q94" s="11"/>
+      <c r="Q94" s="13"/>
       <c r="R94" s="9"/>
-      <c r="S94" s="10"/>
+      <c r="S94" s="12"/>
       <c r="T94" s="9"/>
-      <c r="U94" s="11"/>
+      <c r="U94" s="13"/>
       <c r="V94" s="9"/>
-      <c r="W94" s="10"/>
+      <c r="W94" s="12"/>
       <c r="X94" s="9"/>
-      <c r="Y94" s="11"/>
+      <c r="Y94" s="13"/>
       <c r="Z94" s="9"/>
       <c r="AA94" s="9"/>
       <c r="AB94" s="9"/>
@@ -5086,31 +5282,31 @@
       <c r="AU94" s="9"/>
     </row>
     <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="9"/>
+      <c r="A95" s="11"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
-      <c r="D95" s="11"/>
+      <c r="D95" s="13"/>
       <c r="E95" s="9"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
       <c r="I95" s="9"/>
-      <c r="J95" s="10"/>
+      <c r="J95" s="12"/>
       <c r="K95" s="9"/>
       <c r="L95" s="9"/>
       <c r="M95" s="9"/>
       <c r="N95" s="9"/>
-      <c r="O95" s="10"/>
+      <c r="O95" s="12"/>
       <c r="P95" s="9"/>
-      <c r="Q95" s="11"/>
+      <c r="Q95" s="13"/>
       <c r="R95" s="9"/>
-      <c r="S95" s="10"/>
+      <c r="S95" s="12"/>
       <c r="T95" s="9"/>
-      <c r="U95" s="11"/>
+      <c r="U95" s="13"/>
       <c r="V95" s="9"/>
-      <c r="W95" s="10"/>
+      <c r="W95" s="12"/>
       <c r="X95" s="9"/>
-      <c r="Y95" s="11"/>
+      <c r="Y95" s="13"/>
       <c r="Z95" s="9"/>
       <c r="AA95" s="9"/>
       <c r="AB95" s="9"/>
@@ -5135,31 +5331,31 @@
       <c r="AU95" s="9"/>
     </row>
     <row r="96" ht="32" customHeight="1">
-      <c r="A96" s="9"/>
+      <c r="A96" s="11"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
-      <c r="D96" s="11"/>
+      <c r="D96" s="13"/>
       <c r="E96" s="9"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
       <c r="I96" s="9"/>
-      <c r="J96" s="10"/>
+      <c r="J96" s="12"/>
       <c r="K96" s="9"/>
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
       <c r="N96" s="9"/>
-      <c r="O96" s="10"/>
+      <c r="O96" s="12"/>
       <c r="P96" s="9"/>
-      <c r="Q96" s="11"/>
+      <c r="Q96" s="13"/>
       <c r="R96" s="9"/>
-      <c r="S96" s="10"/>
+      <c r="S96" s="12"/>
       <c r="T96" s="9"/>
-      <c r="U96" s="11"/>
+      <c r="U96" s="13"/>
       <c r="V96" s="9"/>
-      <c r="W96" s="10"/>
+      <c r="W96" s="12"/>
       <c r="X96" s="9"/>
-      <c r="Y96" s="11"/>
+      <c r="Y96" s="13"/>
       <c r="Z96" s="9"/>
       <c r="AA96" s="9"/>
       <c r="AB96" s="9"/>
@@ -5184,31 +5380,31 @@
       <c r="AU96" s="9"/>
     </row>
     <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="9"/>
+      <c r="A97" s="11"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="11"/>
+      <c r="D97" s="13"/>
       <c r="E97" s="9"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
       <c r="I97" s="9"/>
-      <c r="J97" s="10"/>
+      <c r="J97" s="12"/>
       <c r="K97" s="9"/>
       <c r="L97" s="9"/>
       <c r="M97" s="9"/>
       <c r="N97" s="9"/>
-      <c r="O97" s="10"/>
+      <c r="O97" s="12"/>
       <c r="P97" s="9"/>
-      <c r="Q97" s="11"/>
+      <c r="Q97" s="13"/>
       <c r="R97" s="9"/>
-      <c r="S97" s="10"/>
+      <c r="S97" s="12"/>
       <c r="T97" s="9"/>
-      <c r="U97" s="11"/>
+      <c r="U97" s="13"/>
       <c r="V97" s="9"/>
-      <c r="W97" s="10"/>
+      <c r="W97" s="12"/>
       <c r="X97" s="9"/>
-      <c r="Y97" s="11"/>
+      <c r="Y97" s="13"/>
       <c r="Z97" s="9"/>
       <c r="AA97" s="9"/>
       <c r="AB97" s="9"/>
@@ -5233,31 +5429,31 @@
       <c r="AU97" s="9"/>
     </row>
     <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="9"/>
+      <c r="A98" s="11"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
-      <c r="D98" s="11"/>
+      <c r="D98" s="13"/>
       <c r="E98" s="9"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="10"/>
-      <c r="H98" s="10"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
       <c r="I98" s="9"/>
-      <c r="J98" s="10"/>
+      <c r="J98" s="12"/>
       <c r="K98" s="9"/>
       <c r="L98" s="9"/>
       <c r="M98" s="9"/>
       <c r="N98" s="9"/>
-      <c r="O98" s="10"/>
+      <c r="O98" s="12"/>
       <c r="P98" s="9"/>
-      <c r="Q98" s="11"/>
+      <c r="Q98" s="13"/>
       <c r="R98" s="9"/>
-      <c r="S98" s="10"/>
+      <c r="S98" s="12"/>
       <c r="T98" s="9"/>
-      <c r="U98" s="11"/>
+      <c r="U98" s="13"/>
       <c r="V98" s="9"/>
-      <c r="W98" s="10"/>
+      <c r="W98" s="12"/>
       <c r="X98" s="9"/>
-      <c r="Y98" s="11"/>
+      <c r="Y98" s="13"/>
       <c r="Z98" s="9"/>
       <c r="AA98" s="9"/>
       <c r="AB98" s="9"/>
@@ -5282,31 +5478,31 @@
       <c r="AU98" s="9"/>
     </row>
     <row r="99" ht="32" customHeight="1">
-      <c r="A99" s="9"/>
+      <c r="A99" s="11"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
-      <c r="D99" s="11"/>
+      <c r="D99" s="13"/>
       <c r="E99" s="9"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
       <c r="I99" s="9"/>
-      <c r="J99" s="10"/>
+      <c r="J99" s="12"/>
       <c r="K99" s="9"/>
       <c r="L99" s="9"/>
       <c r="M99" s="9"/>
       <c r="N99" s="9"/>
-      <c r="O99" s="10"/>
+      <c r="O99" s="12"/>
       <c r="P99" s="9"/>
-      <c r="Q99" s="11"/>
+      <c r="Q99" s="13"/>
       <c r="R99" s="9"/>
-      <c r="S99" s="10"/>
+      <c r="S99" s="12"/>
       <c r="T99" s="9"/>
-      <c r="U99" s="11"/>
+      <c r="U99" s="13"/>
       <c r="V99" s="9"/>
-      <c r="W99" s="10"/>
+      <c r="W99" s="12"/>
       <c r="X99" s="9"/>
-      <c r="Y99" s="11"/>
+      <c r="Y99" s="13"/>
       <c r="Z99" s="9"/>
       <c r="AA99" s="9"/>
       <c r="AB99" s="9"/>
@@ -5331,31 +5527,31 @@
       <c r="AU99" s="9"/>
     </row>
     <row r="100" ht="32" customHeight="1">
-      <c r="A100" s="9"/>
+      <c r="A100" s="11"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="11"/>
+      <c r="D100" s="13"/>
       <c r="E100" s="9"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
       <c r="I100" s="9"/>
-      <c r="J100" s="10"/>
+      <c r="J100" s="12"/>
       <c r="K100" s="9"/>
       <c r="L100" s="9"/>
       <c r="M100" s="9"/>
       <c r="N100" s="9"/>
-      <c r="O100" s="10"/>
+      <c r="O100" s="12"/>
       <c r="P100" s="9"/>
-      <c r="Q100" s="11"/>
+      <c r="Q100" s="13"/>
       <c r="R100" s="9"/>
-      <c r="S100" s="10"/>
+      <c r="S100" s="12"/>
       <c r="T100" s="9"/>
-      <c r="U100" s="11"/>
+      <c r="U100" s="13"/>
       <c r="V100" s="9"/>
-      <c r="W100" s="10"/>
+      <c r="W100" s="12"/>
       <c r="X100" s="9"/>
-      <c r="Y100" s="11"/>
+      <c r="Y100" s="13"/>
       <c r="Z100" s="9"/>
       <c r="AA100" s="9"/>
       <c r="AB100" s="9"/>
@@ -5380,31 +5576,31 @@
       <c r="AU100" s="9"/>
     </row>
     <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="9"/>
+      <c r="A101" s="11"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
-      <c r="D101" s="11"/>
+      <c r="D101" s="13"/>
       <c r="E101" s="9"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
       <c r="I101" s="9"/>
-      <c r="J101" s="10"/>
+      <c r="J101" s="12"/>
       <c r="K101" s="9"/>
       <c r="L101" s="9"/>
       <c r="M101" s="9"/>
       <c r="N101" s="9"/>
-      <c r="O101" s="10"/>
+      <c r="O101" s="12"/>
       <c r="P101" s="9"/>
-      <c r="Q101" s="11"/>
+      <c r="Q101" s="13"/>
       <c r="R101" s="9"/>
-      <c r="S101" s="10"/>
+      <c r="S101" s="12"/>
       <c r="T101" s="9"/>
-      <c r="U101" s="11"/>
+      <c r="U101" s="13"/>
       <c r="V101" s="9"/>
-      <c r="W101" s="10"/>
+      <c r="W101" s="12"/>
       <c r="X101" s="9"/>
-      <c r="Y101" s="11"/>
+      <c r="Y101" s="13"/>
       <c r="Z101" s="9"/>
       <c r="AA101" s="9"/>
       <c r="AB101" s="9"/>
@@ -5504,7 +5700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5558,628 +5754,628 @@
   </cols>
   <sheetData>
     <row r="1" ht="58" customHeight="1">
-      <c r="A1" s="4" t="str">
-        <v>Employee code</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>Business unit</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>Pay type</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>Effective date</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>Amount unit</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>Approved basic pay / fee</v>
-      </c>
-      <c r="G1" s="5" t="str">
-        <v>Existing de minimis</v>
-      </c>
-      <c r="H1" s="5" t="str">
-        <v>Existing reimbursable</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <v>Salary arrangement</v>
-      </c>
-      <c r="J1" s="6" t="str">
-        <v>Agreed net amount</v>
-      </c>
-      <c r="K1" s="6" t="str">
-        <v>Arrangement document</v>
-      </c>
-      <c r="L1" s="6" t="str">
-        <v>Tax treatment</v>
-      </c>
-      <c r="M1" s="6" t="str">
-        <v>Exemption / tax basis</v>
-      </c>
-      <c r="N1" s="5" t="str">
-        <v>Extra 1 name</v>
-      </c>
-      <c r="O1" s="5" t="str">
-        <v>Extra 1 amount</v>
-      </c>
-      <c r="P1" s="5" t="str">
-        <v>Extra 1 frequency</v>
-      </c>
-      <c r="Q1" s="5" t="str">
-        <v>Extra 1 payable date</v>
-      </c>
-      <c r="R1" s="5" t="str">
-        <v>Extra 2 name</v>
-      </c>
-      <c r="S1" s="5" t="str">
-        <v>Extra 2 amount</v>
-      </c>
-      <c r="T1" s="5" t="str">
-        <v>Extra 2 frequency</v>
-      </c>
-      <c r="U1" s="5" t="str">
-        <v>Extra 2 payable date</v>
-      </c>
-      <c r="V1" s="5" t="str">
-        <v>Extra 3 name</v>
-      </c>
-      <c r="W1" s="5" t="str">
-        <v>Extra 3 amount</v>
-      </c>
-      <c r="X1" s="5" t="str">
-        <v>Extra 3 frequency</v>
-      </c>
-      <c r="Y1" s="5" t="str">
-        <v>Extra 3 payable date</v>
-      </c>
-      <c r="Z1" s="7" t="str">
-        <v>Salary source</v>
-      </c>
-      <c r="AA1" s="7" t="str">
-        <v>PAN ID (if applicable)</v>
-      </c>
-      <c r="AB1" s="7" t="str">
-        <v>Source document / note</v>
-      </c>
-      <c r="AC1" s="7" t="str">
-        <v>Reason for this record</v>
-      </c>
-      <c r="AD1" s="7" t="str">
-        <v>Consultant agreement</v>
-      </c>
-      <c r="AE1" s="7" t="str">
-        <v>Consultant tax document</v>
-      </c>
-      <c r="AF1" s="8" t="str">
-        <v>Employee name</v>
-      </c>
-      <c r="AG1" s="8" t="str">
-        <v>Engagement type</v>
-      </c>
-      <c r="AH1" s="8" t="str">
-        <v>Pay frequency</v>
-      </c>
-      <c r="AI1" s="8" t="str">
-        <v>Gross/net arrangement</v>
-      </c>
-      <c r="AJ1" s="8" t="str">
-        <v>Tax responsibility</v>
-      </c>
-      <c r="AK1" s="8" t="str">
-        <v>Tax coverage scope</v>
-      </c>
-      <c r="AL1" s="8" t="str">
-        <v>Benefit responsibility</v>
-      </c>
-      <c r="AM1" s="8" t="str">
-        <v>Component type</v>
-      </c>
-      <c r="AN1" s="8" t="str">
-        <v>Component name</v>
-      </c>
-      <c r="AO1" s="8" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="AP1" s="8" t="str">
-        <v>Frequency</v>
-      </c>
-      <c r="AQ1" s="8" t="str">
-        <v>Tax treatment detail</v>
-      </c>
-      <c r="AR1" s="8" t="str">
-        <v>Receipt required</v>
-      </c>
-      <c r="AS1" s="8" t="str">
-        <v>Receipt or document reference</v>
-      </c>
-      <c r="AT1" s="8" t="str">
-        <v>Policy reference</v>
-      </c>
-      <c r="AU1" s="8" t="str">
-        <v>Notes</v>
+      <c r="A1" s="8" t="str">
+        <v>Employee code*</v>
+      </c>
+      <c r="B1" s="8" t="str">
+        <v>Business unit*</v>
+      </c>
+      <c r="C1" s="8" t="str">
+        <v>Pay type*</v>
+      </c>
+      <c r="D1" s="8" t="str">
+        <v>Effective date*</v>
+      </c>
+      <c r="E1" s="8" t="str">
+        <v>Amount unit*</v>
+      </c>
+      <c r="F1" s="8" t="str">
+        <v>Approved basic pay / fee*</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>Existing de minimis (optional)</v>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v>Existing reimbursable (optional)</v>
+      </c>
+      <c r="I1" s="10" t="str">
+        <v>Salary arrangement (optional)</v>
+      </c>
+      <c r="J1" s="10" t="str">
+        <v>Agreed net amount (optional)</v>
+      </c>
+      <c r="K1" s="10" t="str">
+        <v>Arrangement document (optional)</v>
+      </c>
+      <c r="L1" s="10" t="str">
+        <v>Tax treatment (optional)</v>
+      </c>
+      <c r="M1" s="10" t="str">
+        <v>Exemption / tax basis (optional)</v>
+      </c>
+      <c r="N1" s="10" t="str">
+        <v>Extra 1 name (optional)</v>
+      </c>
+      <c r="O1" s="10" t="str">
+        <v>Extra 1 amount (optional)</v>
+      </c>
+      <c r="P1" s="10" t="str">
+        <v>Extra 1 frequency (optional)</v>
+      </c>
+      <c r="Q1" s="10" t="str">
+        <v>Extra 1 payable date (optional)</v>
+      </c>
+      <c r="R1" s="10" t="str">
+        <v>Extra 2 name (optional)</v>
+      </c>
+      <c r="S1" s="10" t="str">
+        <v>Extra 2 amount (optional)</v>
+      </c>
+      <c r="T1" s="10" t="str">
+        <v>Extra 2 frequency (optional)</v>
+      </c>
+      <c r="U1" s="10" t="str">
+        <v>Extra 2 payable date (optional)</v>
+      </c>
+      <c r="V1" s="10" t="str">
+        <v>Extra 3 name (optional)</v>
+      </c>
+      <c r="W1" s="10" t="str">
+        <v>Extra 3 amount (optional)</v>
+      </c>
+      <c r="X1" s="10" t="str">
+        <v>Extra 3 frequency (optional)</v>
+      </c>
+      <c r="Y1" s="10" t="str">
+        <v>Extra 3 payable date (optional)</v>
+      </c>
+      <c r="Z1" s="8" t="str">
+        <v>Salary source*</v>
+      </c>
+      <c r="AA1" s="10" t="str">
+        <v>PAN ID (if applicable) (optional)</v>
+      </c>
+      <c r="AB1" s="10" t="str">
+        <v>Source document / note (optional)</v>
+      </c>
+      <c r="AC1" s="8" t="str">
+        <v>Reason for this record*</v>
+      </c>
+      <c r="AD1" s="10" t="str">
+        <v>Consultant agreement (optional)</v>
+      </c>
+      <c r="AE1" s="10" t="str">
+        <v>Consultant tax document (optional)</v>
+      </c>
+      <c r="AF1" s="10" t="str">
+        <v>Employee name (optional)</v>
+      </c>
+      <c r="AG1" s="10" t="str">
+        <v>Engagement type (optional)</v>
+      </c>
+      <c r="AH1" s="10" t="str">
+        <v>Pay frequency (optional)</v>
+      </c>
+      <c r="AI1" s="10" t="str">
+        <v>Gross/net arrangement (optional)</v>
+      </c>
+      <c r="AJ1" s="10" t="str">
+        <v>Tax responsibility (optional)</v>
+      </c>
+      <c r="AK1" s="10" t="str">
+        <v>Tax coverage scope (optional)</v>
+      </c>
+      <c r="AL1" s="10" t="str">
+        <v>Benefit responsibility (optional)</v>
+      </c>
+      <c r="AM1" s="10" t="str">
+        <v>Component type (optional)</v>
+      </c>
+      <c r="AN1" s="10" t="str">
+        <v>Component name (optional)</v>
+      </c>
+      <c r="AO1" s="10" t="str">
+        <v>Amount (optional)</v>
+      </c>
+      <c r="AP1" s="10" t="str">
+        <v>Frequency (optional)</v>
+      </c>
+      <c r="AQ1" s="10" t="str">
+        <v>Tax treatment detail (optional)</v>
+      </c>
+      <c r="AR1" s="10" t="str">
+        <v>Receipt required (optional)</v>
+      </c>
+      <c r="AS1" s="10" t="str">
+        <v>Receipt or document reference (optional)</v>
+      </c>
+      <c r="AT1" s="10" t="str">
+        <v>Policy reference (optional)</v>
+      </c>
+      <c r="AU1" s="10" t="str">
+        <v>Notes (optional)</v>
       </c>
     </row>
     <row r="2" ht="62" customHeight="1">
-      <c r="A2" s="18" t="str">
-        <v>TNG-EXAMPLE-001</v>
-      </c>
-      <c r="B2" s="18" t="str">
+      <c r="A2" s="22" t="str">
+        <v>DEMO-001</v>
+      </c>
+      <c r="B2" s="23" t="str">
         <v>The Fun Roof</v>
       </c>
-      <c r="C2" s="18" t="str">
+      <c r="C2" s="23" t="str">
         <v>Employee salary</v>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="E2" s="18" t="str">
+      <c r="E2" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="F2" s="20" t="n">
+      <c r="F2" s="25" t="n">
         <v>25000</v>
       </c>
-      <c r="G2" s="20" t="n">
+      <c r="G2" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="20" t="n">
+      <c r="H2" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="18" t="str">
+      <c r="I2" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="18" t="str"/>
-      <c r="L2" s="18" t="str">
+      <c r="J2" s="25"/>
+      <c r="K2" s="23" t="str"/>
+      <c r="L2" s="23" t="str">
         <v>Normal tax calculation</v>
       </c>
-      <c r="M2" s="18" t="str"/>
-      <c r="N2" s="18" t="str">
+      <c r="M2" s="23" t="str"/>
+      <c r="N2" s="23" t="str">
         <v>Meal allowance</v>
       </c>
-      <c r="O2" s="20" t="n">
+      <c r="O2" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="P2" s="18" t="str">
+      <c r="P2" s="23" t="str">
         <v>Recurring</v>
       </c>
-      <c r="Q2" s="19" t="str"/>
-      <c r="R2" s="18" t="str"/>
-      <c r="S2" s="20" t="str"/>
-      <c r="T2" s="18" t="str"/>
-      <c r="U2" s="19" t="str"/>
-      <c r="V2" s="18" t="str"/>
-      <c r="W2" s="20" t="str"/>
-      <c r="X2" s="18" t="str"/>
-      <c r="Y2" s="19" t="str"/>
-      <c r="Z2" s="18" t="str">
+      <c r="Q2" s="24" t="str"/>
+      <c r="R2" s="23" t="str"/>
+      <c r="S2" s="25" t="str"/>
+      <c r="T2" s="23" t="str"/>
+      <c r="U2" s="24" t="str"/>
+      <c r="V2" s="23" t="str"/>
+      <c r="W2" s="25" t="str"/>
+      <c r="X2" s="23" t="str"/>
+      <c r="Y2" s="24" t="str"/>
+      <c r="Z2" s="23" t="str">
         <v>Current HRIS record</v>
       </c>
-      <c r="AA2" s="18" t="str"/>
-      <c r="AB2" s="18" t="str">
+      <c r="AA2" s="23" t="str"/>
+      <c r="AB2" s="23" t="str">
         <v>Replace with actual document</v>
       </c>
-      <c r="AC2" s="18" t="str">
+      <c r="AC2" s="23" t="str">
         <v>Example only - replace with approved facts</v>
       </c>
-      <c r="AD2" s="18" t="str"/>
-      <c r="AE2" s="18" t="str"/>
-      <c r="AF2" s="18" t="str">
+      <c r="AD2" s="23" t="str"/>
+      <c r="AE2" s="23" t="str"/>
+      <c r="AF2" s="23" t="str">
         <v>Example employee</v>
       </c>
-      <c r="AG2" s="18" t="str">
+      <c r="AG2" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AH2" s="18" t="str">
+      <c r="AH2" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="AI2" s="18" t="str">
+      <c r="AI2" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="AJ2" s="18" t="str">
+      <c r="AJ2" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AK2" s="18" t="str">
+      <c r="AK2" s="23" t="str">
         <v>Entire package</v>
       </c>
-      <c r="AL2" s="18" t="str">
+      <c r="AL2" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AM2" s="18" t="str"/>
-      <c r="AN2" s="18" t="str"/>
-      <c r="AO2" s="18" t="str"/>
-      <c r="AP2" s="18" t="str"/>
-      <c r="AQ2" s="18" t="str"/>
-      <c r="AR2" s="18" t="str"/>
-      <c r="AS2" s="18" t="str"/>
-      <c r="AT2" s="18" t="str"/>
-      <c r="AU2" s="18" t="str">
+      <c r="AM2" s="23" t="str"/>
+      <c r="AN2" s="23" t="str"/>
+      <c r="AO2" s="23" t="str"/>
+      <c r="AP2" s="23" t="str"/>
+      <c r="AQ2" s="23" t="str"/>
+      <c r="AR2" s="23" t="str"/>
+      <c r="AS2" s="23" t="str"/>
+      <c r="AT2" s="23" t="str"/>
+      <c r="AU2" s="23" t="str">
         <v>Sample only</v>
       </c>
     </row>
     <row r="3" ht="62" customHeight="1">
-      <c r="A3" s="18" t="str">
-        <v>TNG-EXAMPLE-002</v>
-      </c>
-      <c r="B3" s="18" t="str">
+      <c r="A3" s="22" t="str">
+        <v>DEMO-002</v>
+      </c>
+      <c r="B3" s="23" t="str">
         <v>The Fun Roof</v>
       </c>
-      <c r="C3" s="18" t="str">
+      <c r="C3" s="23" t="str">
         <v>Employee salary</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="E3" s="18" t="str">
+      <c r="E3" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F3" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="G3" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="H3" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="23" t="str">
         <v>Company pays income tax</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J3" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="23" t="str">
         <v>Approved agreement / sample only</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="23" t="str">
         <v>Normal tax calculation</v>
       </c>
-      <c r="M3" s="18" t="str"/>
-      <c r="N3" s="18" t="str"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="18" t="str"/>
-      <c r="Q3" s="19" t="str"/>
-      <c r="R3" s="18" t="str"/>
-      <c r="S3" s="20" t="str"/>
-      <c r="T3" s="18" t="str"/>
-      <c r="U3" s="19" t="str"/>
-      <c r="V3" s="18" t="str"/>
-      <c r="W3" s="20" t="str"/>
-      <c r="X3" s="18" t="str"/>
-      <c r="Y3" s="19" t="str"/>
-      <c r="Z3" s="18" t="str">
+      <c r="M3" s="23" t="str"/>
+      <c r="N3" s="23" t="str"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="23" t="str"/>
+      <c r="Q3" s="24" t="str"/>
+      <c r="R3" s="23" t="str"/>
+      <c r="S3" s="25" t="str"/>
+      <c r="T3" s="23" t="str"/>
+      <c r="U3" s="24" t="str"/>
+      <c r="V3" s="23" t="str"/>
+      <c r="W3" s="25" t="str"/>
+      <c r="X3" s="23" t="str"/>
+      <c r="Y3" s="24" t="str"/>
+      <c r="Z3" s="23" t="str">
         <v>Current HRIS record</v>
       </c>
-      <c r="AA3" s="18" t="str"/>
-      <c r="AB3" s="18" t="str">
+      <c r="AA3" s="23" t="str"/>
+      <c r="AB3" s="23" t="str">
         <v>Replace with actual document</v>
       </c>
-      <c r="AC3" s="18" t="str">
+      <c r="AC3" s="23" t="str">
         <v>Example only - replace with approved facts</v>
       </c>
-      <c r="AD3" s="18" t="str"/>
-      <c r="AE3" s="18" t="str"/>
-      <c r="AF3" s="18" t="str">
+      <c r="AD3" s="23" t="str"/>
+      <c r="AE3" s="23" t="str"/>
+      <c r="AF3" s="23" t="str">
         <v>Example employee</v>
       </c>
-      <c r="AG3" s="18" t="str">
+      <c r="AG3" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AH3" s="18" t="str">
+      <c r="AH3" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="AI3" s="18" t="str">
+      <c r="AI3" s="23" t="str">
         <v>Company pays income tax</v>
       </c>
-      <c r="AJ3" s="18" t="str">
+      <c r="AJ3" s="23" t="str">
         <v>Employer</v>
       </c>
-      <c r="AK3" s="18" t="str">
+      <c r="AK3" s="23" t="str">
         <v>Entire package</v>
       </c>
-      <c r="AL3" s="18" t="str">
+      <c r="AL3" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AM3" s="18" t="str"/>
-      <c r="AN3" s="18" t="str"/>
-      <c r="AO3" s="18" t="str"/>
-      <c r="AP3" s="18" t="str"/>
-      <c r="AQ3" s="18" t="str"/>
-      <c r="AR3" s="18" t="str"/>
-      <c r="AS3" s="18" t="str"/>
-      <c r="AT3" s="18" t="str"/>
-      <c r="AU3" s="18" t="str">
+      <c r="AM3" s="23" t="str"/>
+      <c r="AN3" s="23" t="str"/>
+      <c r="AO3" s="23" t="str"/>
+      <c r="AP3" s="23" t="str"/>
+      <c r="AQ3" s="23" t="str"/>
+      <c r="AR3" s="23" t="str"/>
+      <c r="AS3" s="23" t="str"/>
+      <c r="AT3" s="23" t="str"/>
+      <c r="AU3" s="23" t="str">
         <v>Sample only</v>
       </c>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="18" t="str">
-        <v>TNG-EXAMPLE-003</v>
-      </c>
-      <c r="B4" s="18" t="str">
+      <c r="A4" s="22" t="str">
+        <v>DEMO-003</v>
+      </c>
+      <c r="B4" s="23" t="str">
         <v>The Fun Roof</v>
       </c>
-      <c r="C4" s="18" t="str">
+      <c r="C4" s="23" t="str">
         <v>Employee salary</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="E4" s="18" t="str">
+      <c r="E4" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="18" t="str">
+      <c r="I4" s="23" t="str">
         <v>Company pays income tax and employee contributions</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="K4" s="18" t="str">
+      <c r="K4" s="23" t="str">
         <v>Approved agreement / sample only</v>
       </c>
-      <c r="L4" s="18" t="str">
+      <c r="L4" s="23" t="str">
         <v>Normal tax calculation</v>
       </c>
-      <c r="M4" s="18" t="str"/>
-      <c r="N4" s="18" t="str"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="18" t="str"/>
-      <c r="Q4" s="19" t="str"/>
-      <c r="R4" s="18" t="str"/>
-      <c r="S4" s="20" t="str"/>
-      <c r="T4" s="18" t="str"/>
-      <c r="U4" s="19" t="str"/>
-      <c r="V4" s="18" t="str"/>
-      <c r="W4" s="20" t="str"/>
-      <c r="X4" s="18" t="str"/>
-      <c r="Y4" s="19" t="str"/>
-      <c r="Z4" s="18" t="str">
+      <c r="M4" s="23" t="str"/>
+      <c r="N4" s="23" t="str"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="23" t="str"/>
+      <c r="Q4" s="24" t="str"/>
+      <c r="R4" s="23" t="str"/>
+      <c r="S4" s="25" t="str"/>
+      <c r="T4" s="23" t="str"/>
+      <c r="U4" s="24" t="str"/>
+      <c r="V4" s="23" t="str"/>
+      <c r="W4" s="25" t="str"/>
+      <c r="X4" s="23" t="str"/>
+      <c r="Y4" s="24" t="str"/>
+      <c r="Z4" s="23" t="str">
         <v>Current HRIS record</v>
       </c>
-      <c r="AA4" s="18" t="str"/>
-      <c r="AB4" s="18" t="str">
+      <c r="AA4" s="23" t="str"/>
+      <c r="AB4" s="23" t="str">
         <v>Replace with actual document</v>
       </c>
-      <c r="AC4" s="18" t="str">
+      <c r="AC4" s="23" t="str">
         <v>Example only - replace with approved facts</v>
       </c>
-      <c r="AD4" s="18" t="str"/>
-      <c r="AE4" s="18" t="str"/>
-      <c r="AF4" s="18" t="str">
+      <c r="AD4" s="23" t="str"/>
+      <c r="AE4" s="23" t="str"/>
+      <c r="AF4" s="23" t="str">
         <v>Example employee</v>
       </c>
-      <c r="AG4" s="18" t="str">
+      <c r="AG4" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AH4" s="18" t="str">
+      <c r="AH4" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="AI4" s="18" t="str">
+      <c r="AI4" s="23" t="str">
         <v>Company pays income tax and employee contributions</v>
       </c>
-      <c r="AJ4" s="18" t="str">
+      <c r="AJ4" s="23" t="str">
         <v>Employer</v>
       </c>
-      <c r="AK4" s="18" t="str">
+      <c r="AK4" s="23" t="str">
         <v>Entire package</v>
       </c>
-      <c r="AL4" s="18" t="str">
+      <c r="AL4" s="23" t="str">
         <v>Employer</v>
       </c>
-      <c r="AM4" s="18" t="str"/>
-      <c r="AN4" s="18" t="str"/>
-      <c r="AO4" s="18" t="str"/>
-      <c r="AP4" s="18" t="str"/>
-      <c r="AQ4" s="18" t="str"/>
-      <c r="AR4" s="18" t="str"/>
-      <c r="AS4" s="18" t="str"/>
-      <c r="AT4" s="18" t="str"/>
-      <c r="AU4" s="18" t="str">
+      <c r="AM4" s="23" t="str"/>
+      <c r="AN4" s="23" t="str"/>
+      <c r="AO4" s="23" t="str"/>
+      <c r="AP4" s="23" t="str"/>
+      <c r="AQ4" s="23" t="str"/>
+      <c r="AR4" s="23" t="str"/>
+      <c r="AS4" s="23" t="str"/>
+      <c r="AT4" s="23" t="str"/>
+      <c r="AU4" s="23" t="str">
         <v>Sample only</v>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="18" t="str">
-        <v>TNG-EXAMPLE-004</v>
-      </c>
-      <c r="B5" s="18" t="str">
+      <c r="A5" s="22" t="str">
+        <v>DEMO-004</v>
+      </c>
+      <c r="B5" s="23" t="str">
         <v>The Fun Roof</v>
       </c>
-      <c r="C5" s="18" t="str">
+      <c r="C5" s="23" t="str">
         <v>Employee salary</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="E5" s="18" t="str">
+      <c r="E5" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="18" t="str">
+      <c r="I5" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="18" t="str"/>
-      <c r="L5" s="18" t="str">
+      <c r="J5" s="25"/>
+      <c r="K5" s="23" t="str"/>
+      <c r="L5" s="23" t="str">
         <v>Normal tax calculation</v>
       </c>
-      <c r="M5" s="18" t="str"/>
-      <c r="N5" s="18" t="str"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="18" t="str"/>
-      <c r="Q5" s="19" t="str"/>
-      <c r="R5" s="18" t="str"/>
-      <c r="S5" s="20" t="str"/>
-      <c r="T5" s="18" t="str"/>
-      <c r="U5" s="19" t="str"/>
-      <c r="V5" s="18" t="str"/>
-      <c r="W5" s="20" t="str"/>
-      <c r="X5" s="18" t="str"/>
-      <c r="Y5" s="19" t="str"/>
-      <c r="Z5" s="18" t="str">
+      <c r="M5" s="23" t="str"/>
+      <c r="N5" s="23" t="str"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="23" t="str"/>
+      <c r="Q5" s="24" t="str"/>
+      <c r="R5" s="23" t="str"/>
+      <c r="S5" s="25" t="str"/>
+      <c r="T5" s="23" t="str"/>
+      <c r="U5" s="24" t="str"/>
+      <c r="V5" s="23" t="str"/>
+      <c r="W5" s="25" t="str"/>
+      <c r="X5" s="23" t="str"/>
+      <c r="Y5" s="24" t="str"/>
+      <c r="Z5" s="23" t="str">
         <v>Current HRIS record</v>
       </c>
-      <c r="AA5" s="18" t="str"/>
-      <c r="AB5" s="18" t="str">
+      <c r="AA5" s="23" t="str"/>
+      <c r="AB5" s="23" t="str">
         <v>Replace with actual document</v>
       </c>
-      <c r="AC5" s="18" t="str">
+      <c r="AC5" s="23" t="str">
         <v>Example only - replace with approved facts</v>
       </c>
-      <c r="AD5" s="18" t="str"/>
-      <c r="AE5" s="18" t="str"/>
-      <c r="AF5" s="18" t="str">
+      <c r="AD5" s="23" t="str"/>
+      <c r="AE5" s="23" t="str"/>
+      <c r="AF5" s="23" t="str">
         <v>Example employee</v>
       </c>
-      <c r="AG5" s="18" t="str">
+      <c r="AG5" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AH5" s="18" t="str">
+      <c r="AH5" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="AI5" s="18" t="str">
+      <c r="AI5" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="AJ5" s="18" t="str">
+      <c r="AJ5" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AK5" s="18" t="str">
+      <c r="AK5" s="23" t="str">
         <v>Entire package</v>
       </c>
-      <c r="AL5" s="18" t="str">
+      <c r="AL5" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AM5" s="18" t="str"/>
-      <c r="AN5" s="18" t="str"/>
-      <c r="AO5" s="18" t="str"/>
-      <c r="AP5" s="18" t="str"/>
-      <c r="AQ5" s="18" t="str"/>
-      <c r="AR5" s="18" t="str"/>
-      <c r="AS5" s="18" t="str"/>
-      <c r="AT5" s="18" t="str"/>
-      <c r="AU5" s="18" t="str">
+      <c r="AM5" s="23" t="str"/>
+      <c r="AN5" s="23" t="str"/>
+      <c r="AO5" s="23" t="str"/>
+      <c r="AP5" s="23" t="str"/>
+      <c r="AQ5" s="23" t="str"/>
+      <c r="AR5" s="23" t="str"/>
+      <c r="AS5" s="23" t="str"/>
+      <c r="AT5" s="23" t="str"/>
+      <c r="AU5" s="23" t="str">
         <v>Sample only</v>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="18" t="str">
-        <v>TNG-EXAMPLE-004</v>
-      </c>
-      <c r="B6" s="18" t="str">
+      <c r="A6" s="22" t="str">
+        <v>DEMO-004</v>
+      </c>
+      <c r="B6" s="23" t="str">
         <v>The Fun Roof</v>
       </c>
-      <c r="C6" s="18" t="str">
+      <c r="C6" s="23" t="str">
         <v>Consultant fee</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="25" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="18" t="str">
+      <c r="I6" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="J6" s="20"/>
-      <c r="K6" s="18" t="str"/>
-      <c r="L6" s="18" t="str">
+      <c r="J6" s="25"/>
+      <c r="K6" s="23" t="str"/>
+      <c r="L6" s="23" t="str">
         <v>Normal tax calculation</v>
       </c>
-      <c r="M6" s="18" t="str"/>
-      <c r="N6" s="18" t="str">
+      <c r="M6" s="23" t="str"/>
+      <c r="N6" s="23" t="str">
         <v>Project completion fee</v>
       </c>
-      <c r="O6" s="20" t="n">
+      <c r="O6" s="25" t="n">
         <v>5000</v>
       </c>
-      <c r="P6" s="18" t="str">
+      <c r="P6" s="23" t="str">
         <v>One time</v>
       </c>
-      <c r="Q6" s="19" t="n">
+      <c r="Q6" s="24" t="n">
         <v>46371</v>
       </c>
-      <c r="R6" s="18" t="str"/>
-      <c r="S6" s="20" t="str"/>
-      <c r="T6" s="18" t="str"/>
-      <c r="U6" s="19" t="str"/>
-      <c r="V6" s="18" t="str"/>
-      <c r="W6" s="20" t="str"/>
-      <c r="X6" s="18" t="str"/>
-      <c r="Y6" s="19" t="str"/>
-      <c r="Z6" s="18" t="str">
+      <c r="R6" s="23" t="str"/>
+      <c r="S6" s="25" t="str"/>
+      <c r="T6" s="23" t="str"/>
+      <c r="U6" s="24" t="str"/>
+      <c r="V6" s="23" t="str"/>
+      <c r="W6" s="25" t="str"/>
+      <c r="X6" s="23" t="str"/>
+      <c r="Y6" s="24" t="str"/>
+      <c r="Z6" s="23" t="str">
         <v>Approved consultant agreement</v>
       </c>
-      <c r="AA6" s="18" t="str"/>
-      <c r="AB6" s="18" t="str">
+      <c r="AA6" s="23" t="str"/>
+      <c r="AB6" s="23" t="str">
         <v>Replace with actual document</v>
       </c>
-      <c r="AC6" s="18" t="str">
+      <c r="AC6" s="23" t="str">
         <v>Example only - replace with approved facts</v>
       </c>
-      <c r="AD6" s="18" t="str">
+      <c r="AD6" s="23" t="str">
         <v>CONSULTING-SAMPLE-003</v>
       </c>
-      <c r="AE6" s="18" t="str">
+      <c r="AE6" s="23" t="str">
         <v>REVIEWED-TAX-SAMPLE-003</v>
       </c>
-      <c r="AF6" s="18" t="str">
+      <c r="AF6" s="23" t="str">
         <v>Example employee</v>
       </c>
-      <c r="AG6" s="18" t="str">
+      <c r="AG6" s="23" t="str">
         <v>Consultant</v>
       </c>
-      <c r="AH6" s="18" t="str">
+      <c r="AH6" s="23" t="str">
         <v>Monthly</v>
       </c>
-      <c r="AI6" s="18" t="str">
+      <c r="AI6" s="23" t="str">
         <v>Gross salary</v>
       </c>
-      <c r="AJ6" s="18" t="str">
+      <c r="AJ6" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AK6" s="18" t="str">
+      <c r="AK6" s="23" t="str">
         <v>Entire package</v>
       </c>
-      <c r="AL6" s="18" t="str">
+      <c r="AL6" s="23" t="str">
         <v>Employee</v>
       </c>
-      <c r="AM6" s="18" t="str"/>
-      <c r="AN6" s="18" t="str"/>
-      <c r="AO6" s="18" t="str"/>
-      <c r="AP6" s="18" t="str"/>
-      <c r="AQ6" s="18" t="str"/>
-      <c r="AR6" s="18" t="str"/>
-      <c r="AS6" s="18" t="str">
+      <c r="AM6" s="23" t="str"/>
+      <c r="AN6" s="23" t="str"/>
+      <c r="AO6" s="23" t="str"/>
+      <c r="AP6" s="23" t="str"/>
+      <c r="AQ6" s="23" t="str"/>
+      <c r="AR6" s="23" t="str"/>
+      <c r="AS6" s="23" t="str">
         <v>CONSULTING-SAMPLE-003</v>
       </c>
-      <c r="AT6" s="18" t="str"/>
-      <c r="AU6" s="18" t="str">
+      <c r="AT6" s="23" t="str"/>
+      <c r="AU6" s="23" t="str">
         <v>Sample only</v>
       </c>
     </row>
@@ -6259,187 +6455,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="110" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="56" customHeight="1">
-      <c r="A1" s="4" t="str">
-        <v>PAY INPUT — FILL ONE TAB ONLY</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>How to use this workbook</v>
-      </c>
-    </row>
-    <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="21" t="str">
-        <v>START HERE</v>
-      </c>
-      <c r="B2" s="21" t="str">
-        <v>Fill Pay Input only. Field Guide explains EVERY field and gives exact choices/examples. Use Examples as a guide; replace sample details with approved facts. Upload on Payroll → Pay Packages, review the preview, then save drafts. Never relabel a net agreement as Gross.</v>
-      </c>
-    </row>
-    <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="21" t="str">
-        <v>1. Use Pay Input</v>
-      </c>
-      <c r="B3" s="21" t="str">
-        <v>One continuous row contains employee, salary, net/gross agreement and allowances. No package keys. Examples and this Guide are NOT imported.</v>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="21" t="str">
-        <v>2. Approved basic pay / fee</v>
-      </c>
-      <c r="B4" s="21" t="str">
-        <v>Copy the amount and unit from Current HRIS / approved PAN or consultant agreement. Do not change approved basic salary to a guessed gross-up.</v>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="21" t="str">
-        <v>3. Existing allowances</v>
-      </c>
-      <c r="B5" s="21" t="str">
-        <v>Enter the existing HRIS de minimis and reimbursable amounts in their own columns. They must match the source; a de minimis name alone does not make it tax exempt.</v>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="21" t="str">
-        <v>4. Extra allowances</v>
-      </c>
-      <c r="B6" s="21" t="str">
-        <v>Extra 1–3 are optional. Choose a suggested name or type a custom name and amount. Recurring uses the package amount unit. One time needs a payable date. Do not repeat existing allowances here.</v>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="21" t="str">
-        <v>5. Gross salary</v>
-      </c>
-      <c r="B7" s="21" t="str">
-        <v>Agreed amount is before employee contributions and withholding. Leave Agreed net amount blank. Employer statutory shares are always separate company costs.</v>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="21" t="str">
-        <v>6. Net — covers tax</v>
-      </c>
-      <c r="B8" s="21" t="str">
-        <v>Company funds enough additional taxable compensation to meet the target before employee statutory shares. Employee shares and other authorized deductions still reduce payout.</v>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="21" t="str">
-        <v>7. Net — covers tax + shares</v>
-      </c>
-      <c r="B9" s="21" t="str">
-        <v>Company funds enough additional taxable compensation to meet the target after tax and employee statutory shares, before loans and other deductions.</v>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="21" t="str">
-        <v>8. Agreed net amount</v>
-      </c>
-      <c r="B10" s="21" t="str">
-        <v>Enter the approved target in the Amount unit of this row, separately from approved basic pay. Give the agreement reference. Finance reviews the target for each cutoff, including attendance and included allowances.</v>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="21" t="str">
-        <v>9. Tax exemption</v>
-      </c>
-      <c r="B11" s="21" t="str">
-        <v>Use Exemption requested only with legal basis and evidence. HR/Finance must classify applicable amounts and limits. Net salary does NOT exempt someone from tax. Custom rules are not automatically calculated.</v>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="21" t="str">
-        <v>10. Dual employee + consultant</v>
-      </c>
-      <c r="B12" s="21" t="str">
-        <v>Use the same employee code in two rows: Employee salary and Consultant fee. Give the consultant agreement and tax document on the consultant row. Contractor withholding remains separate. See the last two example rows.</v>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="21" t="str">
-        <v>11. Documents, not invented IDs</v>
-      </c>
-      <c r="B13" s="21" t="str">
-        <v>Type a real agreement/PAN/document reference or descriptive source note. Only PAN ID requires the actual approved HRIS PAN UUID; leave it blank for Current HRIS.</v>
-      </c>
-    </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="21" t="str">
-        <v>12. Dropdowns and custom text</v>
-      </c>
-      <c r="B14" s="21" t="str">
-        <v>Dropdowns suggest common choices. You may type custom allowance names, notes and document references. Employee codes and BUs must match HRIS. For different salary/tax rules choose Custom - needs review and document the terms.</v>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="21" t="str">
-        <v>13. Import and check</v>
-      </c>
-      <c r="B15" s="21" t="str">
-        <v>Payroll → Pay Packages → upload. Check every preview row before Save drafts. Importing neither approves pay nor releases payment. Old two-tab workbooks are still supported.</v>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="21" t="str">
-        <v>14. Employer cost</v>
-      </c>
-      <c r="B16" s="21" t="str">
-        <v>Total company payroll cost = gross compensation (including company-funded gross-up) + employer statutory shares. Do not add withholding or employee contributions again; those are already inside gross.</v>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="21" t="str">
-        <v>15. Finance net calculation</v>
-      </c>
-      <c r="B17" s="21" t="str">
-        <v>Finance must confirm final monthly statutory bases including the applicable treatment of gross-up. Net calculation uses those reviewed bases and the reviewed BIR/YTD method. Recalculate if bases change; unsupported FBT cases need separate review.</v>
-      </c>
-    </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="21" t="str">
-        <v>BIR withholding table</v>
-      </c>
-      <c r="B18" s="21" t="str">
-        <v>https://bir-cdn.bir.gov.ph/local/pdf/Annex%20E%20RR%2011-2018.pdf</v>
-      </c>
-    </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="21" t="str">
-        <v>BIR tax / exemption rules</v>
-      </c>
-      <c r="B19" s="21" t="str">
-        <v>https://bir-cdn.bir.gov.ph/local/pdf/Digest%20RR%2011-2018.pdf</v>
-      </c>
-    </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="21" t="str">
-        <v>SSS contribution schedule</v>
-      </c>
-      <c r="B20" s="21" t="str">
-        <v>https://www.sss.gov.ph/sss-contribution-table/</v>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="21" t="str">
-        <v>PhilHealth employer procedure</v>
-      </c>
-      <c r="B21" s="21" t="str">
-        <v>https://www.philhealth.gov.ph/partners/employers/pay_procedures.php</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6465,660 +6480,660 @@
       </c>
     </row>
     <row r="2" ht="76" customHeight="1">
-      <c r="A2" s="21" t="str">
+      <c r="A2" s="26" t="str">
         <v>Employee code</v>
       </c>
-      <c r="B2" s="21" t="str">
+      <c r="B2" s="26" t="str">
         <v>Required</v>
       </c>
-      <c r="C2" s="21" t="str">
+      <c r="C2" s="26" t="str">
         <v>Copy from Employee codes you can access on the upload page. Do not invent an ID. Missing employee? Register in HRIS first.</v>
       </c>
-      <c r="D2" s="21" t="str">
-        <v>TNG-EXAMPLE-001 (example only)</v>
+      <c r="D2" s="26" t="str">
+        <v>DEMO-001 (example only)</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="26" t="str">
         <v>Business unit</v>
       </c>
-      <c r="B3" s="21" t="str">
+      <c r="B3" s="26" t="str">
         <v>Required dropdown</v>
       </c>
-      <c r="C3" s="21" t="str">
+      <c r="C3" s="26" t="str">
         <v>Choose the employee payroll group exactly as listed.</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="26" t="str">
         <v>The Fun Roof</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="26" t="str">
         <v>Pay type</v>
       </c>
-      <c r="B4" s="21" t="str">
+      <c r="B4" s="26" t="str">
         <v>Required dropdown</v>
       </c>
-      <c r="C4" s="21" t="str">
+      <c r="C4" s="26" t="str">
         <v>Employee salary; a separate consulting engagement needs another row.</v>
       </c>
-      <c r="D4" s="21" t="str">
+      <c r="D4" s="26" t="str">
         <v>Employee salary</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="26" t="str">
         <v>Effective date</v>
       </c>
-      <c r="B5" s="21" t="str">
+      <c r="B5" s="26" t="str">
         <v>Required date</v>
       </c>
-      <c r="C5" s="21" t="str">
+      <c r="C5" s="26" t="str">
         <v>Actual approved start date of this pay arrangement, not automatically the hire date.</v>
       </c>
-      <c r="D5" s="21" t="str">
+      <c r="D5" s="26" t="str">
         <v>2026-09-01</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="26" t="str">
         <v>Amount unit</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="26" t="str">
         <v>Required dropdown</v>
       </c>
-      <c r="C6" s="21" t="str">
+      <c r="C6" s="26" t="str">
         <v>Basis of the approved amount. Daily/hourly is not monthly salary.</v>
       </c>
-      <c r="D6" s="21" t="str">
+      <c r="D6" s="26" t="str">
         <v>Monthly</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="26" t="str">
         <v>Approved basic pay / fee</v>
       </c>
-      <c r="B7" s="21" t="str">
+      <c r="B7" s="26" t="str">
         <v>Required amount</v>
       </c>
-      <c r="C7" s="21" t="str">
+      <c r="C7" s="26" t="str">
         <v>Copy approved basic pay from HRIS/PAN. Do not replace it with guessed gross-up.</v>
       </c>
-      <c r="D7" s="21" t="str">
+      <c r="D7" s="26" t="str">
         <v>25000</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="26" t="str">
         <v>Existing de minimis</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="26" t="str">
         <v>If recorded in HRIS</v>
       </c>
-      <c r="C8" s="21" t="str">
+      <c r="C8" s="26" t="str">
         <v>Must exactly match the existing approved allowance; do not repeat under Extras.</v>
       </c>
-      <c r="D8" s="21" t="str">
+      <c r="D8" s="26" t="str">
         <v>1500 (example only)</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="26" t="str">
         <v>Existing reimbursable</v>
       </c>
-      <c r="B9" s="21" t="str">
+      <c r="B9" s="26" t="str">
         <v>If recorded in HRIS</v>
       </c>
-      <c r="C9" s="21" t="str">
+      <c r="C9" s="26" t="str">
         <v>Must exactly match HRIS/PAN; blank means none in this upload.</v>
       </c>
-      <c r="D9" s="21" t="str">
+      <c r="D9" s="26" t="str">
         <v>1000 (example only)</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="26" t="str">
         <v>Salary arrangement</v>
       </c>
-      <c r="B10" s="21" t="str">
+      <c r="B10" s="26" t="str">
         <v>Required dropdown</v>
       </c>
-      <c r="C10" s="21" t="str">
+      <c r="C10" s="26" t="str">
         <v>Gross salary = employee deductions apply. Company pays income tax = tax covered only. Company pays income tax and employee contributions = both covered.</v>
       </c>
-      <c r="D10" s="21" t="str">
+      <c r="D10" s="26" t="str">
         <v>Choose the approved arrangement</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="26" t="str">
         <v>Agreed net amount</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="26" t="str">
         <v>Net arrangements only</v>
       </c>
-      <c r="C11" s="21" t="str">
+      <c r="C11" s="26" t="str">
         <v>Approved target for this payment unit. Tax-only target is before employee contributions; tax-plus-contributions target is after both, before loans/other deductions.</v>
       </c>
-      <c r="D11" s="21" t="str">
+      <c r="D11" s="26" t="str">
         <v>30000 (example only)</v>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="26" t="str">
         <v>Arrangement document</v>
       </c>
-      <c r="B12" s="21" t="str">
+      <c r="B12" s="26" t="str">
         <v>Net/custom only</v>
       </c>
-      <c r="C12" s="21" t="str">
+      <c r="C12" s="26" t="str">
         <v>Approved JO, PAN or signed agreement explicitly stating net terms. Enter title/reference and date. A generic JO without net terms is insufficient.</v>
       </c>
-      <c r="D12" s="21" t="str">
+      <c r="D12" s="26" t="str">
         <v>Approved JO for [employee], [date], section [x] confirming tax coverage</v>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="21" t="str">
+      <c r="A13" s="26" t="str">
         <v>Tax treatment</v>
       </c>
-      <c r="B13" s="21" t="str">
+      <c r="B13" s="26" t="str">
         <v>Dropdown; blank = normal</v>
       </c>
-      <c r="C13" s="21" t="str">
+      <c r="C13" s="26" t="str">
         <v>Choose Normal tax calculation even when company pays tax. Exemption requires a genuine separate basis and evidence.</v>
       </c>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="26" t="str">
         <v>Normal tax calculation</v>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="21" t="str">
+      <c r="A14" s="26" t="str">
         <v>Exemption / tax basis</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="26" t="str">
         <v>Only exemption/custom</v>
       </c>
-      <c r="C14" s="21" t="str">
+      <c r="C14" s="26" t="str">
         <v>Actual supporting basis and document; do not use net salary as the basis.</v>
       </c>
-      <c r="D14" s="21" t="str">
+      <c r="D14" s="26" t="str">
         <v>Leave blank for normal tax calculation</v>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="21" t="str">
+      <c r="A15" s="26" t="str">
         <v>Extra 1 name</v>
       </c>
-      <c r="B15" s="21" t="str">
+      <c r="B15" s="26" t="str">
         <v>Optional dropdown or custom</v>
       </c>
-      <c r="C15" s="21" t="str">
+      <c r="C15" s="26" t="str">
         <v>Name an additional approved component. Do not repeat existing allowances.</v>
       </c>
-      <c r="D15" s="21" t="str">
+      <c r="D15" s="26" t="str">
         <v>Meal allowance</v>
       </c>
     </row>
     <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="21" t="str">
+      <c r="A16" s="26" t="str">
         <v>Extra 1 amount</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="26" t="str">
         <v>When Extra name is filled</v>
       </c>
-      <c r="C16" s="21" t="str">
+      <c r="C16" s="26" t="str">
         <v>Approved component amount.</v>
       </c>
-      <c r="D16" s="21" t="str">
+      <c r="D16" s="26" t="str">
         <v>1000 (example only)</v>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="21" t="str">
+      <c r="A17" s="26" t="str">
         <v>Extra 1 frequency</v>
       </c>
-      <c r="B17" s="21" t="str">
+      <c r="B17" s="26" t="str">
         <v>Dropdown</v>
       </c>
-      <c r="C17" s="21" t="str">
+      <c r="C17" s="26" t="str">
         <v>Recurring uses the package amount unit. One time requires a payable date.</v>
       </c>
-      <c r="D17" s="21" t="str">
+      <c r="D17" s="26" t="str">
         <v>Recurring</v>
       </c>
     </row>
     <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="21" t="str">
+      <c r="A18" s="26" t="str">
         <v>Extra 1 payable date</v>
       </c>
-      <c r="B18" s="21" t="str">
+      <c r="B18" s="26" t="str">
         <v>One time only</v>
       </c>
-      <c r="C18" s="21" t="str">
+      <c r="C18" s="26" t="str">
         <v>Approved payment date. Leave blank for recurring.</v>
       </c>
-      <c r="D18" s="21" t="str">
+      <c r="D18" s="26" t="str">
         <v>2026-12-15</v>
       </c>
     </row>
     <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="21" t="str">
+      <c r="A19" s="26" t="str">
         <v>Extra 2 name</v>
       </c>
-      <c r="B19" s="21" t="str">
+      <c r="B19" s="26" t="str">
         <v>Optional dropdown or custom</v>
       </c>
-      <c r="C19" s="21" t="str">
+      <c r="C19" s="26" t="str">
         <v>Name an additional approved component. Do not repeat existing allowances.</v>
       </c>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="26" t="str">
         <v>Meal allowance</v>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1">
-      <c r="A20" s="21" t="str">
+      <c r="A20" s="26" t="str">
         <v>Extra 2 amount</v>
       </c>
-      <c r="B20" s="21" t="str">
+      <c r="B20" s="26" t="str">
         <v>When Extra name is filled</v>
       </c>
-      <c r="C20" s="21" t="str">
+      <c r="C20" s="26" t="str">
         <v>Approved component amount.</v>
       </c>
-      <c r="D20" s="21" t="str">
+      <c r="D20" s="26" t="str">
         <v>1000 (example only)</v>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="21" t="str">
+      <c r="A21" s="26" t="str">
         <v>Extra 2 frequency</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="26" t="str">
         <v>Dropdown</v>
       </c>
-      <c r="C21" s="21" t="str">
+      <c r="C21" s="26" t="str">
         <v>Recurring uses the package amount unit. One time requires a payable date.</v>
       </c>
-      <c r="D21" s="21" t="str">
+      <c r="D21" s="26" t="str">
         <v>Recurring</v>
       </c>
     </row>
     <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="21" t="str">
+      <c r="A22" s="26" t="str">
         <v>Extra 2 payable date</v>
       </c>
-      <c r="B22" s="21" t="str">
+      <c r="B22" s="26" t="str">
         <v>One time only</v>
       </c>
-      <c r="C22" s="21" t="str">
+      <c r="C22" s="26" t="str">
         <v>Approved payment date. Leave blank for recurring.</v>
       </c>
-      <c r="D22" s="21" t="str">
+      <c r="D22" s="26" t="str">
         <v>2026-12-15</v>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="21" t="str">
+      <c r="A23" s="26" t="str">
         <v>Extra 3 name</v>
       </c>
-      <c r="B23" s="21" t="str">
+      <c r="B23" s="26" t="str">
         <v>Optional dropdown or custom</v>
       </c>
-      <c r="C23" s="21" t="str">
+      <c r="C23" s="26" t="str">
         <v>Name an additional approved component. Do not repeat existing allowances.</v>
       </c>
-      <c r="D23" s="21" t="str">
+      <c r="D23" s="26" t="str">
         <v>Meal allowance</v>
       </c>
     </row>
     <row r="24" ht="76" customHeight="1">
-      <c r="A24" s="21" t="str">
+      <c r="A24" s="26" t="str">
         <v>Extra 3 amount</v>
       </c>
-      <c r="B24" s="21" t="str">
+      <c r="B24" s="26" t="str">
         <v>When Extra name is filled</v>
       </c>
-      <c r="C24" s="21" t="str">
+      <c r="C24" s="26" t="str">
         <v>Approved component amount.</v>
       </c>
-      <c r="D24" s="21" t="str">
+      <c r="D24" s="26" t="str">
         <v>1000 (example only)</v>
       </c>
     </row>
     <row r="25" ht="76" customHeight="1">
-      <c r="A25" s="21" t="str">
+      <c r="A25" s="26" t="str">
         <v>Extra 3 frequency</v>
       </c>
-      <c r="B25" s="21" t="str">
+      <c r="B25" s="26" t="str">
         <v>Dropdown</v>
       </c>
-      <c r="C25" s="21" t="str">
+      <c r="C25" s="26" t="str">
         <v>Recurring uses the package amount unit. One time requires a payable date.</v>
       </c>
-      <c r="D25" s="21" t="str">
+      <c r="D25" s="26" t="str">
         <v>Recurring</v>
       </c>
     </row>
     <row r="26" ht="76" customHeight="1">
-      <c r="A26" s="21" t="str">
+      <c r="A26" s="26" t="str">
         <v>Extra 3 payable date</v>
       </c>
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="26" t="str">
         <v>One time only</v>
       </c>
-      <c r="C26" s="21" t="str">
+      <c r="C26" s="26" t="str">
         <v>Approved payment date. Leave blank for recurring.</v>
       </c>
-      <c r="D26" s="21" t="str">
+      <c r="D26" s="26" t="str">
         <v>2026-12-15</v>
       </c>
     </row>
     <row r="27" ht="76" customHeight="1">
-      <c r="A27" s="21" t="str">
+      <c r="A27" s="26" t="str">
         <v>Salary source</v>
       </c>
-      <c r="B27" s="21" t="str">
+      <c r="B27" s="26" t="str">
         <v>Required dropdown</v>
       </c>
-      <c r="C27" s="21" t="str">
+      <c r="C27" s="26" t="str">
         <v>Where approved salary comes from.</v>
       </c>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="26" t="str">
         <v>Current HRIS record</v>
       </c>
     </row>
     <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="21" t="str">
+      <c r="A28" s="26" t="str">
         <v>PAN ID (if applicable)</v>
       </c>
-      <c r="B28" s="21" t="str">
+      <c r="B28" s="26" t="str">
         <v>Approved PAN only</v>
       </c>
-      <c r="C28" s="21" t="str">
+      <c r="C28" s="26" t="str">
         <v>Copy actual PAN record ID from HRIS; otherwise leave blank.</v>
       </c>
-      <c r="D28" s="21" t="str">
+      <c r="D28" s="26" t="str">
         <v>Leave blank for Current HRIS record</v>
       </c>
     </row>
     <row r="29" ht="76" customHeight="1">
-      <c r="A29" s="21" t="str">
+      <c r="A29" s="26" t="str">
         <v>Source document / note</v>
       </c>
-      <c r="B29" s="21" t="str">
+      <c r="B29" s="26" t="str">
         <v>Optional descriptive text</v>
       </c>
-      <c r="C29" s="21" t="str">
+      <c r="C29" s="26" t="str">
         <v>Actual source reference. Blank uses Salary source.</v>
       </c>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="26" t="str">
         <v>Current HRIS record checked on [date]</v>
       </c>
     </row>
     <row r="30" ht="76" customHeight="1">
-      <c r="A30" s="21" t="str">
+      <c r="A30" s="26" t="str">
         <v>Reason for this record</v>
       </c>
-      <c r="B30" s="21" t="str">
+      <c r="B30" s="26" t="str">
         <v>Required dropdown or text</v>
       </c>
-      <c r="C30" s="21" t="str">
+      <c r="C30" s="26" t="str">
         <v>Why this package is being recorded.</v>
       </c>
-      <c r="D30" s="21" t="str">
+      <c r="D30" s="26" t="str">
         <v>Initial setup</v>
       </c>
     </row>
     <row r="31" ht="76" customHeight="1">
-      <c r="A31" s="21" t="str">
+      <c r="A31" s="26" t="str">
         <v>Consultant agreement</v>
       </c>
-      <c r="B31" s="21" t="str">
+      <c r="B31" s="26" t="str">
         <v>Consultant row only</v>
       </c>
-      <c r="C31" s="21" t="str">
+      <c r="C31" s="26" t="str">
         <v>Actual distinct consulting engagement reference, not employee salary agreement.</v>
       </c>
-      <c r="D31" s="21" t="str">
+      <c r="D31" s="26" t="str">
         <v>Signed consulting agreement [reference/date]</v>
       </c>
     </row>
     <row r="32" ht="76" customHeight="1">
-      <c r="A32" s="21" t="str">
+      <c r="A32" s="26" t="str">
         <v>Consultant tax document</v>
       </c>
-      <c r="B32" s="21" t="str">
+      <c r="B32" s="26" t="str">
         <v>Consultant row only</v>
       </c>
-      <c r="C32" s="21" t="str">
+      <c r="C32" s="26" t="str">
         <v>Actual reviewed consultant withholding/tax-profile reference.</v>
       </c>
-      <c r="D32" s="21" t="str">
+      <c r="D32" s="26" t="str">
         <v>Finance-reviewed tax profile [reference]</v>
       </c>
     </row>
     <row r="33" ht="76" customHeight="1">
-      <c r="A33" s="21" t="str">
+      <c r="A33" s="26" t="str">
         <v>Employee name</v>
       </c>
-      <c r="B33" s="21" t="str">
+      <c r="B33" s="26" t="str">
         <v>Optional check</v>
       </c>
-      <c r="C33" s="21" t="str">
+      <c r="C33" s="26" t="str">
         <v>Employee display name for human review; Employee code remains the system key.</v>
       </c>
-      <c r="D33" s="21" t="str">
+      <c r="D33" s="26" t="str">
         <v>Example employee</v>
       </c>
     </row>
     <row r="34" ht="76" customHeight="1">
-      <c r="A34" s="21" t="str">
+      <c r="A34" s="26" t="str">
         <v>Engagement type</v>
       </c>
-      <c r="B34" s="21" t="str">
+      <c r="B34" s="26" t="str">
         <v>Optional dropdown</v>
       </c>
-      <c r="C34" s="21" t="str">
+      <c r="C34" s="26" t="str">
         <v>Employee or Consultant. Pay type remains the authoritative stream.</v>
       </c>
-      <c r="D34" s="21" t="str">
+      <c r="D34" s="26" t="str">
         <v>Employee</v>
       </c>
     </row>
     <row r="35" ht="76" customHeight="1">
-      <c r="A35" s="21" t="str">
+      <c r="A35" s="26" t="str">
         <v>Pay frequency</v>
       </c>
-      <c r="B35" s="21" t="str">
+      <c r="B35" s="26" t="str">
         <v>Optional dropdown</v>
       </c>
-      <c r="C35" s="21" t="str">
+      <c r="C35" s="26" t="str">
         <v>Monthly, Daily, Hourly, Per invoice, or another approved frequency.</v>
       </c>
-      <c r="D35" s="21" t="str">
+      <c r="D35" s="26" t="str">
         <v>Monthly</v>
       </c>
     </row>
     <row r="36" ht="76" customHeight="1">
-      <c r="A36" s="21" t="str">
+      <c r="A36" s="26" t="str">
         <v>Gross/net arrangement</v>
       </c>
-      <c r="B36" s="21" t="str">
+      <c r="B36" s="26" t="str">
         <v>Optional structured choice</v>
       </c>
-      <c r="C36" s="21" t="str">
+      <c r="C36" s="26" t="str">
         <v>Use the four approved package-basis choices; do not describe gross/net terms only in Notes.</v>
       </c>
-      <c r="D36" s="21" t="str">
+      <c r="D36" s="26" t="str">
         <v>Gross pay</v>
       </c>
     </row>
     <row r="37" ht="76" customHeight="1">
-      <c r="A37" s="21" t="str">
+      <c r="A37" s="26" t="str">
         <v>Tax responsibility</v>
       </c>
-      <c r="B37" s="21" t="str">
+      <c r="B37" s="26" t="str">
         <v>Optional structured choice</v>
       </c>
-      <c r="C37" s="21" t="str">
+      <c r="C37" s="26" t="str">
         <v>Who funds income tax: Employee, Employer, or Split.</v>
       </c>
-      <c r="D37" s="21" t="str">
+      <c r="D37" s="26" t="str">
         <v>Employee</v>
       </c>
     </row>
     <row r="38" ht="76" customHeight="1">
-      <c r="A38" s="21" t="str">
+      <c r="A38" s="26" t="str">
         <v>Tax coverage scope</v>
       </c>
-      <c r="B38" s="21" t="str">
+      <c r="B38" s="26" t="str">
         <v>Optional structured choice</v>
       </c>
-      <c r="C38" s="21" t="str">
+      <c r="C38" s="26" t="str">
         <v>Basic pay only, Selected components, or Entire package.</v>
       </c>
-      <c r="D38" s="21" t="str">
+      <c r="D38" s="26" t="str">
         <v>Entire package</v>
       </c>
     </row>
     <row r="39" ht="76" customHeight="1">
-      <c r="A39" s="21" t="str">
+      <c r="A39" s="26" t="str">
         <v>Benefit responsibility</v>
       </c>
-      <c r="B39" s="21" t="str">
+      <c r="B39" s="26" t="str">
         <v>Optional structured choice</v>
       </c>
-      <c r="C39" s="21" t="str">
+      <c r="C39" s="26" t="str">
         <v>Who funds employee benefit shares: Employee, Employer, or Split.</v>
       </c>
-      <c r="D39" s="21" t="str">
+      <c r="D39" s="26" t="str">
         <v>Employee</v>
       </c>
     </row>
     <row r="40" ht="76" customHeight="1">
-      <c r="A40" s="21" t="str">
+      <c r="A40" s="26" t="str">
         <v>Component type</v>
       </c>
-      <c r="B40" s="21" t="str">
+      <c r="B40" s="26" t="str">
         <v>Optional component detail</v>
       </c>
-      <c r="C40" s="21" t="str">
+      <c r="C40" s="26" t="str">
         <v>Classify the component so payroll can apply the correct evidence and cost rules.</v>
       </c>
-      <c r="D40" s="21" t="str">
+      <c r="D40" s="26" t="str">
         <v>Fixed allowance</v>
       </c>
     </row>
     <row r="41" ht="76" customHeight="1">
-      <c r="A41" s="21" t="str">
+      <c r="A41" s="26" t="str">
         <v>Component name</v>
       </c>
-      <c r="B41" s="21" t="str">
+      <c r="B41" s="26" t="str">
         <v>When a component is supplied</v>
       </c>
-      <c r="C41" s="21" t="str">
+      <c r="C41" s="26" t="str">
         <v>Approved component name.</v>
       </c>
-      <c r="D41" s="21" t="str">
+      <c r="D41" s="26" t="str">
         <v>Meal allowance</v>
       </c>
     </row>
     <row r="42" ht="76" customHeight="1">
-      <c r="A42" s="21" t="str">
+      <c r="A42" s="26" t="str">
         <v>Amount</v>
       </c>
-      <c r="B42" s="21" t="str">
+      <c r="B42" s="26" t="str">
         <v>When a component is supplied</v>
       </c>
-      <c r="C42" s="21" t="str">
+      <c r="C42" s="26" t="str">
         <v>Approved amount or maximum amount.</v>
       </c>
-      <c r="D42" s="21" t="str">
+      <c r="D42" s="26" t="str">
         <v>1000</v>
       </c>
     </row>
     <row r="43" ht="76" customHeight="1">
-      <c r="A43" s="21" t="str">
+      <c r="A43" s="26" t="str">
         <v>Frequency</v>
       </c>
-      <c r="B43" s="21" t="str">
+      <c r="B43" s="26" t="str">
         <v>When a component is supplied</v>
       </c>
-      <c r="C43" s="21" t="str">
+      <c r="C43" s="26" t="str">
         <v>Approved component frequency.</v>
       </c>
-      <c r="D43" s="21" t="str">
+      <c r="D43" s="26" t="str">
         <v>Monthly</v>
       </c>
     </row>
     <row r="44" ht="76" customHeight="1">
-      <c r="A44" s="21" t="str">
+      <c r="A44" s="26" t="str">
         <v>Tax treatment detail</v>
       </c>
-      <c r="B44" s="21" t="str">
+      <c r="B44" s="26" t="str">
         <v>When a component is supplied</v>
       </c>
-      <c r="C44" s="21" t="str">
+      <c r="C44" s="26" t="str">
         <v>Taxable, Non-taxable, Reimbursable, or Needs review.</v>
       </c>
-      <c r="D44" s="21" t="str">
+      <c r="D44" s="26" t="str">
         <v>Taxable</v>
       </c>
     </row>
     <row r="45" ht="76" customHeight="1">
-      <c r="A45" s="21" t="str">
+      <c r="A45" s="26" t="str">
         <v>Receipt required</v>
       </c>
-      <c r="B45" s="21" t="str">
+      <c r="B45" s="26" t="str">
         <v>Reimbursements</v>
       </c>
-      <c r="C45" s="21" t="str">
+      <c r="C45" s="26" t="str">
         <v>Yes prevents inclusion in payable amounts until evidence is approved.</v>
       </c>
-      <c r="D45" s="21" t="str">
+      <c r="D45" s="26" t="str">
         <v>Yes</v>
       </c>
     </row>
     <row r="46" ht="76" customHeight="1">
-      <c r="A46" s="21" t="str">
+      <c r="A46" s="26" t="str">
         <v>Receipt or document reference</v>
       </c>
-      <c r="B46" s="21" t="str">
+      <c r="B46" s="26" t="str">
         <v>When evidence exists</v>
       </c>
-      <c r="C46" s="21" t="str">
+      <c r="C46" s="26" t="str">
         <v>Receipt, invoice, or supporting-document reference.</v>
       </c>
-      <c r="D46" s="21" t="str">
+      <c r="D46" s="26" t="str">
         <v>Receipt 2026-001</v>
       </c>
     </row>
     <row r="47" ht="76" customHeight="1">
-      <c r="A47" s="21" t="str">
+      <c r="A47" s="26" t="str">
         <v>Policy reference</v>
       </c>
-      <c r="B47" s="21" t="str">
+      <c r="B47" s="26" t="str">
         <v>Optional component detail</v>
       </c>
-      <c r="C47" s="21" t="str">
+      <c r="C47" s="26" t="str">
         <v>Policy, limit, or approval source.</v>
       </c>
-      <c r="D47" s="21" t="str">
+      <c r="D47" s="26" t="str">
         <v>Benefits policy 2026</v>
       </c>
     </row>
     <row r="48" ht="76" customHeight="1">
-      <c r="A48" s="21" t="str">
+      <c r="A48" s="26" t="str">
         <v>Notes</v>
       </c>
-      <c r="B48" s="21" t="str">
+      <c r="B48" s="26" t="str">
         <v>Optional</v>
       </c>
-      <c r="C48" s="21" t="str">
+      <c r="C48" s="26" t="str">
         <v>Short clarification that does not replace structured pay, tax, or benefit choices.</v>
       </c>
-      <c r="D48" s="21" t="str">
+      <c r="D48" s="26" t="str">
         <v>Approved by Finance on 2026-09-01</v>
       </c>
     </row>
